--- a/estado/registroRegional.xlsx
+++ b/estado/registroRegional.xlsx
@@ -7875,19 +7875,19 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>755312</v>
+        <v>755256</v>
       </c>
       <c r="C91" t="n">
         <v>0</v>
       </c>
       <c r="D91" s="5" t="n">
-        <v>0</v>
+        <v>-7.414154680449934e-05</v>
       </c>
       <c r="E91" t="n">
         <v>0</v>
       </c>
       <c r="F91" t="n">
-        <v>563776</v>
+        <v>562514</v>
       </c>
       <c r="G91" t="n">
         <v>4444</v>
@@ -7896,13 +7896,13 @@
         <v>28740</v>
       </c>
       <c r="I91" s="5" t="n">
-        <v>0.0002211692480915775</v>
+        <v>-0.001893342805632443</v>
       </c>
       <c r="J91" t="n">
-        <v>40378</v>
+        <v>68997</v>
       </c>
       <c r="K91" t="n">
-        <v>233</v>
+        <v>203</v>
       </c>
     </row>
     <row r="92">
@@ -7912,10 +7912,10 @@
         </is>
       </c>
       <c r="B92" s="6" t="n">
-        <v>133555</v>
+        <v>133499</v>
       </c>
       <c r="F92" s="6" t="n">
-        <v>343115</v>
+        <v>341853</v>
       </c>
       <c r="G92" s="6" t="n">
         <v>4444</v>
@@ -7924,7 +7924,7 @@
         <v>28740</v>
       </c>
       <c r="J92" s="6" t="n">
-        <v>40378</v>
+        <v>68997</v>
       </c>
     </row>
   </sheetData>
@@ -11313,16 +11313,16 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>1062578</v>
+        <v>1062565</v>
       </c>
       <c r="C91" t="n">
         <v>0</v>
       </c>
       <c r="D91" s="5" t="n">
-        <v>0</v>
+        <v>-1.223439596904886e-05</v>
       </c>
       <c r="E91" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F91" t="n">
         <v>756019</v>
@@ -11340,7 +11340,7 @@
         <v>78833</v>
       </c>
       <c r="K91" t="n">
-        <v>619</v>
+        <v>620</v>
       </c>
     </row>
     <row r="92">
@@ -11350,7 +11350,7 @@
         </is>
       </c>
       <c r="B92" s="6" t="n">
-        <v>213152</v>
+        <v>213139</v>
       </c>
       <c r="F92" s="6" t="n">
         <v>257112</v>
@@ -14788,10 +14788,10 @@
         <v>0</v>
       </c>
       <c r="J91" t="n">
-        <v>139445</v>
+        <v>139791</v>
       </c>
       <c r="K91" t="n">
-        <v>352</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
@@ -14813,7 +14813,7 @@
         <v>109913</v>
       </c>
       <c r="J92" s="6" t="n">
-        <v>139445</v>
+        <v>139791</v>
       </c>
     </row>
   </sheetData>
@@ -18202,19 +18202,19 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>1208743</v>
+        <v>1208524</v>
       </c>
       <c r="C91" t="n">
         <v>0</v>
       </c>
       <c r="D91" s="5" t="n">
-        <v>0</v>
+        <v>-0.0001811799530586734</v>
       </c>
       <c r="E91" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F91" t="n">
-        <v>530685</v>
+        <v>530625</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -18223,13 +18223,13 @@
         <v>121658</v>
       </c>
       <c r="I91" s="5" t="n">
-        <v>0</v>
+        <v>-9.197615364923055e-05</v>
       </c>
       <c r="J91" t="n">
         <v>78979</v>
       </c>
       <c r="K91" t="n">
-        <v>300</v>
+        <v>297</v>
       </c>
     </row>
     <row r="92">
@@ -18239,10 +18239,10 @@
         </is>
       </c>
       <c r="B92" s="6" t="n">
-        <v>78680</v>
+        <v>78461</v>
       </c>
       <c r="F92" s="6" t="n">
-        <v>295828</v>
+        <v>295768</v>
       </c>
       <c r="G92" s="6" t="n">
         <v>0</v>
@@ -21649,7 +21649,7 @@
         <v>0.0004131652144401242</v>
       </c>
       <c r="E91" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F91" t="n">
         <v>1840332</v>
@@ -21667,7 +21667,7 @@
         <v>188122</v>
       </c>
       <c r="K91" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="92">
@@ -28516,16 +28516,16 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>934232</v>
+        <v>934221</v>
       </c>
       <c r="C91" t="n">
         <v>11614</v>
       </c>
       <c r="D91" s="5" t="n">
-        <v>0</v>
+        <v>-1.162980020003256e-05</v>
       </c>
       <c r="E91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F91" t="n">
         <v>500298</v>
@@ -28540,10 +28540,10 @@
         <v>0</v>
       </c>
       <c r="J91" t="n">
-        <v>65692</v>
+        <v>65706</v>
       </c>
       <c r="K91" t="n">
-        <v>332</v>
+        <v>315</v>
       </c>
     </row>
     <row r="92">
@@ -28553,7 +28553,7 @@
         </is>
       </c>
       <c r="B92" s="6" t="n">
-        <v>91751</v>
+        <v>91740</v>
       </c>
       <c r="F92" s="6" t="n">
         <v>225386</v>
@@ -28565,7 +28565,7 @@
         <v>120390</v>
       </c>
       <c r="J92" s="6" t="n">
-        <v>65692</v>
+        <v>65706</v>
       </c>
     </row>
   </sheetData>
@@ -31978,10 +31978,10 @@
         <v>0</v>
       </c>
       <c r="J91" t="n">
-        <v>54581</v>
+        <v>54585</v>
       </c>
       <c r="K91" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
@@ -32003,7 +32003,7 @@
         <v>49295</v>
       </c>
       <c r="J92" s="6" t="n">
-        <v>54581</v>
+        <v>54585</v>
       </c>
     </row>
   </sheetData>
@@ -32145,7 +32145,7 @@
         <v>0.349311817750356</v>
       </c>
       <c r="E3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F3" t="n">
         <v>81421</v>
@@ -35404,7 +35404,7 @@
         <v>0</v>
       </c>
       <c r="F91" t="n">
-        <v>348059</v>
+        <v>348031</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -35413,13 +35413,13 @@
         <v>29391</v>
       </c>
       <c r="I91" s="5" t="n">
-        <v>0</v>
+        <v>-7.418201086236587e-05</v>
       </c>
       <c r="J91" t="n">
-        <v>56247</v>
+        <v>56040</v>
       </c>
       <c r="K91" t="n">
-        <v>63</v>
+        <v>88</v>
       </c>
     </row>
     <row r="92">
@@ -35432,7 +35432,7 @@
         <v>255297</v>
       </c>
       <c r="F92" s="6" t="n">
-        <v>266638</v>
+        <v>266610</v>
       </c>
       <c r="G92" s="6" t="n">
         <v>0</v>
@@ -35441,7 +35441,7 @@
         <v>29391</v>
       </c>
       <c r="J92" s="6" t="n">
-        <v>56247</v>
+        <v>56040</v>
       </c>
     </row>
   </sheetData>
@@ -38857,7 +38857,7 @@
         <v>52540</v>
       </c>
       <c r="K91" t="n">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="92">

--- a/estado/registroRegional.xlsx
+++ b/estado/registroRegional.xlsx
@@ -7875,13 +7875,13 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>755256</v>
+        <v>755277</v>
       </c>
       <c r="C91" t="n">
         <v>0</v>
       </c>
       <c r="D91" s="5" t="n">
-        <v>-7.414154680449934e-05</v>
+        <v>-4.633846675281208e-05</v>
       </c>
       <c r="E91" t="n">
         <v>0</v>
@@ -7912,7 +7912,7 @@
         </is>
       </c>
       <c r="B92" s="6" t="n">
-        <v>133499</v>
+        <v>133520</v>
       </c>
       <c r="F92" s="6" t="n">
         <v>341853</v>
@@ -11322,7 +11322,7 @@
         <v>-1.223439596904886e-05</v>
       </c>
       <c r="E91" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F91" t="n">
         <v>756019</v>
@@ -18211,7 +18211,7 @@
         <v>-0.0001811799530586734</v>
       </c>
       <c r="E91" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F91" t="n">
         <v>530625</v>
@@ -21649,25 +21649,25 @@
         <v>0.0004131652144401242</v>
       </c>
       <c r="E91" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="F91" t="n">
-        <v>1840332</v>
+        <v>1840346</v>
       </c>
       <c r="G91" t="n">
         <v>123505</v>
       </c>
       <c r="H91" t="n">
-        <v>127641</v>
+        <v>128091</v>
       </c>
       <c r="I91" s="5" t="n">
-        <v>0</v>
+        <v>0.0002218526802576934</v>
       </c>
       <c r="J91" t="n">
-        <v>188122</v>
+        <v>188212</v>
       </c>
       <c r="K91" t="n">
-        <v>129</v>
+        <v>39</v>
       </c>
     </row>
     <row r="92">
@@ -21680,16 +21680,16 @@
         <v>733881</v>
       </c>
       <c r="F92" s="6" t="n">
-        <v>955868</v>
+        <v>955882</v>
       </c>
       <c r="G92" s="6" t="n">
         <v>123505</v>
       </c>
       <c r="H92" s="6" t="n">
-        <v>127641</v>
+        <v>128091</v>
       </c>
       <c r="J92" s="6" t="n">
-        <v>188122</v>
+        <v>188212</v>
       </c>
     </row>
   </sheetData>
@@ -28525,7 +28525,7 @@
         <v>-1.162980020003256e-05</v>
       </c>
       <c r="E91" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F91" t="n">
         <v>500298</v>
@@ -31963,7 +31963,7 @@
         <v>0</v>
       </c>
       <c r="E91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F91" t="n">
         <v>298111</v>
@@ -35392,13 +35392,13 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>746228</v>
+        <v>746310</v>
       </c>
       <c r="C91" t="n">
         <v>0</v>
       </c>
       <c r="D91" s="5" t="n">
-        <v>0</v>
+        <v>0.0001098859865885494</v>
       </c>
       <c r="E91" t="n">
         <v>0</v>
@@ -35429,7 +35429,7 @@
         </is>
       </c>
       <c r="B92" s="6" t="n">
-        <v>255297</v>
+        <v>255379</v>
       </c>
       <c r="F92" s="6" t="n">
         <v>266610</v>

--- a/estado/registroRegional.xlsx
+++ b/estado/registroRegional.xlsx
@@ -11322,7 +11322,7 @@
         <v>-1.223439596904886e-05</v>
       </c>
       <c r="E91" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F91" t="n">
         <v>756019</v>
@@ -11337,10 +11337,10 @@
         <v>0</v>
       </c>
       <c r="J91" t="n">
-        <v>78833</v>
+        <v>64899</v>
       </c>
       <c r="K91" t="n">
-        <v>620</v>
+        <v>14511</v>
       </c>
     </row>
     <row r="92">
@@ -11362,7 +11362,7 @@
         <v>91062</v>
       </c>
       <c r="J92" s="6" t="n">
-        <v>78833</v>
+        <v>64899</v>
       </c>
     </row>
   </sheetData>
@@ -14764,16 +14764,16 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>1687612</v>
+        <v>1689550</v>
       </c>
       <c r="C91" t="n">
         <v>0</v>
       </c>
       <c r="D91" s="5" t="n">
-        <v>0</v>
+        <v>0.001148368226819909</v>
       </c>
       <c r="E91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F91" t="n">
         <v>1159049</v>
@@ -14801,7 +14801,7 @@
         </is>
       </c>
       <c r="B92" s="6" t="n">
-        <v>480261</v>
+        <v>482199</v>
       </c>
       <c r="F92" s="6" t="n">
         <v>616453</v>
@@ -21640,16 +21640,16 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>3069702</v>
+        <v>3069973</v>
       </c>
       <c r="C91" t="n">
         <v>48983</v>
       </c>
       <c r="D91" s="5" t="n">
-        <v>0.0004131652144401242</v>
+        <v>0.0005000967153044671</v>
       </c>
       <c r="E91" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="F91" t="n">
         <v>1840346</v>
@@ -21677,7 +21677,7 @@
         </is>
       </c>
       <c r="B92" s="6" t="n">
-        <v>733881</v>
+        <v>734152</v>
       </c>
       <c r="F92" s="6" t="n">
         <v>955882</v>
@@ -25087,7 +25087,7 @@
         <v>0</v>
       </c>
       <c r="E91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F91" t="n">
         <v>590365</v>
@@ -31963,19 +31963,19 @@
         <v>0</v>
       </c>
       <c r="E91" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F91" t="n">
-        <v>298111</v>
+        <v>296573</v>
       </c>
       <c r="G91" t="n">
         <v>83</v>
       </c>
       <c r="H91" t="n">
-        <v>49295</v>
+        <v>50701</v>
       </c>
       <c r="I91" s="5" t="n">
-        <v>0</v>
+        <v>-0.0003798681397108973</v>
       </c>
       <c r="J91" t="n">
         <v>54585</v>
@@ -31994,13 +31994,13 @@
         <v>105838</v>
       </c>
       <c r="F92" s="6" t="n">
-        <v>191704</v>
+        <v>190166</v>
       </c>
       <c r="G92" s="6" t="n">
         <v>83</v>
       </c>
       <c r="H92" s="6" t="n">
-        <v>49295</v>
+        <v>50701</v>
       </c>
       <c r="J92" s="6" t="n">
         <v>54585</v>
@@ -38839,7 +38839,7 @@
         <v>0</v>
       </c>
       <c r="E91" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F91" t="n">
         <v>295759</v>

--- a/estado/registroRegional.xlsx
+++ b/estado/registroRegional.xlsx
@@ -11337,10 +11337,10 @@
         <v>0</v>
       </c>
       <c r="J91" t="n">
-        <v>64899</v>
+        <v>72590</v>
       </c>
       <c r="K91" t="n">
-        <v>14511</v>
+        <v>6868</v>
       </c>
     </row>
     <row r="92">
@@ -11362,7 +11362,7 @@
         <v>91062</v>
       </c>
       <c r="J92" s="6" t="n">
-        <v>64899</v>
+        <v>72590</v>
       </c>
     </row>
   </sheetData>
@@ -21649,7 +21649,7 @@
         <v>0.0005000967153044671</v>
       </c>
       <c r="E91" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F91" t="n">
         <v>1840346</v>

--- a/estado/registroRegional.xlsx
+++ b/estado/registroRegional.xlsx
@@ -11322,7 +11322,7 @@
         <v>-1.223439596904886e-05</v>
       </c>
       <c r="E91" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F91" t="n">
         <v>756019</v>

--- a/estado/registroRegional.xlsx
+++ b/estado/registroRegional.xlsx
@@ -7887,7 +7887,7 @@
         <v>0</v>
       </c>
       <c r="F91" t="n">
-        <v>562514</v>
+        <v>562417</v>
       </c>
       <c r="G91" t="n">
         <v>4444</v>
@@ -7896,7 +7896,7 @@
         <v>28740</v>
       </c>
       <c r="I91" s="5" t="n">
-        <v>-0.001893342805632443</v>
+        <v>-0.002055868692487618</v>
       </c>
       <c r="J91" t="n">
         <v>68997</v>
@@ -7915,7 +7915,7 @@
         <v>133520</v>
       </c>
       <c r="F92" s="6" t="n">
-        <v>341853</v>
+        <v>341756</v>
       </c>
       <c r="G92" s="6" t="n">
         <v>4444</v>
@@ -11322,7 +11322,7 @@
         <v>-1.223439596904886e-05</v>
       </c>
       <c r="E91" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F91" t="n">
         <v>756019</v>
@@ -11337,10 +11337,10 @@
         <v>0</v>
       </c>
       <c r="J91" t="n">
-        <v>72590</v>
+        <v>79013</v>
       </c>
       <c r="K91" t="n">
-        <v>6868</v>
+        <v>448</v>
       </c>
     </row>
     <row r="92">
@@ -11362,7 +11362,7 @@
         <v>91062</v>
       </c>
       <c r="J92" s="6" t="n">
-        <v>72590</v>
+        <v>79013</v>
       </c>
     </row>
   </sheetData>
@@ -14773,7 +14773,7 @@
         <v>0.001148368226819909</v>
       </c>
       <c r="E91" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F91" t="n">
         <v>1159049</v>
@@ -18220,10 +18220,10 @@
         <v>0</v>
       </c>
       <c r="H91" t="n">
-        <v>121658</v>
+        <v>122921</v>
       </c>
       <c r="I91" s="5" t="n">
-        <v>-9.197615364923055e-05</v>
+        <v>0.001844121880667072</v>
       </c>
       <c r="J91" t="n">
         <v>78979</v>
@@ -18248,7 +18248,7 @@
         <v>0</v>
       </c>
       <c r="H92" s="6" t="n">
-        <v>121658</v>
+        <v>122921</v>
       </c>
       <c r="J92" s="6" t="n">
         <v>78979</v>
@@ -21640,16 +21640,16 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>3069973</v>
+        <v>3069774</v>
       </c>
       <c r="C91" t="n">
         <v>48983</v>
       </c>
       <c r="D91" s="5" t="n">
-        <v>0.0005000967153044671</v>
+        <v>0.000436261406551684</v>
       </c>
       <c r="E91" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="F91" t="n">
         <v>1840346</v>
@@ -21658,16 +21658,16 @@
         <v>123505</v>
       </c>
       <c r="H91" t="n">
-        <v>128091</v>
+        <v>131537</v>
       </c>
       <c r="I91" s="5" t="n">
-        <v>0.0002218526802576934</v>
+        <v>0.001869491335792201</v>
       </c>
       <c r="J91" t="n">
-        <v>188212</v>
+        <v>188251</v>
       </c>
       <c r="K91" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
@@ -21677,7 +21677,7 @@
         </is>
       </c>
       <c r="B92" s="6" t="n">
-        <v>734152</v>
+        <v>733953</v>
       </c>
       <c r="F92" s="6" t="n">
         <v>955882</v>
@@ -21686,10 +21686,10 @@
         <v>123505</v>
       </c>
       <c r="H92" s="6" t="n">
-        <v>128091</v>
+        <v>131537</v>
       </c>
       <c r="J92" s="6" t="n">
-        <v>188212</v>
+        <v>188251</v>
       </c>
     </row>
   </sheetData>
@@ -28540,10 +28540,10 @@
         <v>0</v>
       </c>
       <c r="J91" t="n">
-        <v>65706</v>
+        <v>65708</v>
       </c>
       <c r="K91" t="n">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="92">
@@ -28565,7 +28565,7 @@
         <v>120390</v>
       </c>
       <c r="J92" s="6" t="n">
-        <v>65706</v>
+        <v>65708</v>
       </c>
     </row>
   </sheetData>
@@ -31963,7 +31963,7 @@
         <v>0</v>
       </c>
       <c r="E91" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F91" t="n">
         <v>296573</v>
@@ -31978,10 +31978,10 @@
         <v>-0.0003798681397108973</v>
       </c>
       <c r="J91" t="n">
-        <v>54585</v>
+        <v>54582</v>
       </c>
       <c r="K91" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="92">
@@ -32003,7 +32003,7 @@
         <v>50701</v>
       </c>
       <c r="J92" s="6" t="n">
-        <v>54585</v>
+        <v>54582</v>
       </c>
     </row>
   </sheetData>
@@ -35401,7 +35401,7 @@
         <v>0.0001098859865885494</v>
       </c>
       <c r="E91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F91" t="n">
         <v>348031</v>
@@ -38839,7 +38839,7 @@
         <v>0</v>
       </c>
       <c r="E91" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F91" t="n">
         <v>295759</v>

--- a/estado/registroRegional.xlsx
+++ b/estado/registroRegional.xlsx
@@ -7887,7 +7887,7 @@
         <v>0</v>
       </c>
       <c r="F91" t="n">
-        <v>562417</v>
+        <v>562497</v>
       </c>
       <c r="G91" t="n">
         <v>4444</v>
@@ -7896,13 +7896,13 @@
         <v>28740</v>
       </c>
       <c r="I91" s="5" t="n">
-        <v>-0.002055868692487618</v>
+        <v>-0.001921826723947268</v>
       </c>
       <c r="J91" t="n">
-        <v>68997</v>
+        <v>69005</v>
       </c>
       <c r="K91" t="n">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="92">
@@ -7915,7 +7915,7 @@
         <v>133520</v>
       </c>
       <c r="F92" s="6" t="n">
-        <v>341756</v>
+        <v>341836</v>
       </c>
       <c r="G92" s="6" t="n">
         <v>4444</v>
@@ -7924,7 +7924,7 @@
         <v>28740</v>
       </c>
       <c r="J92" s="6" t="n">
-        <v>68997</v>
+        <v>69005</v>
       </c>
     </row>
   </sheetData>
@@ -11340,7 +11340,7 @@
         <v>79013</v>
       </c>
       <c r="K91" t="n">
-        <v>448</v>
+        <v>456</v>
       </c>
     </row>
     <row r="92">
@@ -14764,16 +14764,16 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>1689550</v>
+        <v>1690899</v>
       </c>
       <c r="C91" t="n">
         <v>0</v>
       </c>
       <c r="D91" s="5" t="n">
-        <v>0.001148368226819909</v>
+        <v>0.001947722580782786</v>
       </c>
       <c r="E91" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="F91" t="n">
         <v>1159049</v>
@@ -14788,10 +14788,10 @@
         <v>0</v>
       </c>
       <c r="J91" t="n">
-        <v>139791</v>
+        <v>139793</v>
       </c>
       <c r="K91" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="92">
@@ -14801,7 +14801,7 @@
         </is>
       </c>
       <c r="B92" s="6" t="n">
-        <v>482199</v>
+        <v>483548</v>
       </c>
       <c r="F92" s="6" t="n">
         <v>616453</v>
@@ -14813,7 +14813,7 @@
         <v>109913</v>
       </c>
       <c r="J92" s="6" t="n">
-        <v>139791</v>
+        <v>139793</v>
       </c>
     </row>
   </sheetData>
@@ -18202,13 +18202,13 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>1208524</v>
+        <v>1208589</v>
       </c>
       <c r="C91" t="n">
         <v>0</v>
       </c>
       <c r="D91" s="5" t="n">
-        <v>-0.0001811799530586734</v>
+        <v>-0.0001274050811462817</v>
       </c>
       <c r="E91" t="n">
         <v>3</v>
@@ -18229,7 +18229,7 @@
         <v>78979</v>
       </c>
       <c r="K91" t="n">
-        <v>297</v>
+        <v>306</v>
       </c>
     </row>
     <row r="92">
@@ -18239,7 +18239,7 @@
         </is>
       </c>
       <c r="B92" s="6" t="n">
-        <v>78461</v>
+        <v>78526</v>
       </c>
       <c r="F92" s="6" t="n">
         <v>295768</v>
@@ -21640,16 +21640,16 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>3069774</v>
+        <v>3070048</v>
       </c>
       <c r="C91" t="n">
         <v>48983</v>
       </c>
       <c r="D91" s="5" t="n">
-        <v>0.000436261406551684</v>
+        <v>0.0005241552487540086</v>
       </c>
       <c r="E91" t="n">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="F91" t="n">
         <v>1840346</v>
@@ -21658,16 +21658,16 @@
         <v>123505</v>
       </c>
       <c r="H91" t="n">
-        <v>131537</v>
+        <v>131855</v>
       </c>
       <c r="I91" s="5" t="n">
-        <v>0.001869491335792201</v>
+        <v>0.002021536922692947</v>
       </c>
       <c r="J91" t="n">
-        <v>188251</v>
+        <v>188265</v>
       </c>
       <c r="K91" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="92">
@@ -21677,7 +21677,7 @@
         </is>
       </c>
       <c r="B92" s="6" t="n">
-        <v>733953</v>
+        <v>734227</v>
       </c>
       <c r="F92" s="6" t="n">
         <v>955882</v>
@@ -21686,10 +21686,10 @@
         <v>123505</v>
       </c>
       <c r="H92" s="6" t="n">
-        <v>131537</v>
+        <v>131855</v>
       </c>
       <c r="J92" s="6" t="n">
-        <v>188251</v>
+        <v>188265</v>
       </c>
     </row>
   </sheetData>
@@ -25087,7 +25087,7 @@
         <v>0</v>
       </c>
       <c r="E91" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F91" t="n">
         <v>590365</v>
@@ -25105,7 +25105,7 @@
         <v>60875</v>
       </c>
       <c r="K91" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="92">
@@ -28534,16 +28534,16 @@
         <v>6655</v>
       </c>
       <c r="H91" t="n">
-        <v>120390</v>
+        <v>122284</v>
       </c>
       <c r="I91" s="5" t="n">
-        <v>0</v>
+        <v>0.00301908206515415</v>
       </c>
       <c r="J91" t="n">
         <v>65708</v>
       </c>
       <c r="K91" t="n">
-        <v>313</v>
+        <v>325</v>
       </c>
     </row>
     <row r="92">
@@ -28562,7 +28562,7 @@
         <v>6655</v>
       </c>
       <c r="H92" s="6" t="n">
-        <v>120390</v>
+        <v>122284</v>
       </c>
       <c r="J92" s="6" t="n">
         <v>65708</v>
@@ -31954,13 +31954,13 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>799674</v>
+        <v>799733</v>
       </c>
       <c r="C91" t="n">
         <v>0</v>
       </c>
       <c r="D91" s="5" t="n">
-        <v>0</v>
+        <v>7.378006537664098e-05</v>
       </c>
       <c r="E91" t="n">
         <v>4</v>
@@ -31978,10 +31978,10 @@
         <v>-0.0003798681397108973</v>
       </c>
       <c r="J91" t="n">
-        <v>54582</v>
+        <v>54600</v>
       </c>
       <c r="K91" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
@@ -31991,7 +31991,7 @@
         </is>
       </c>
       <c r="B92" s="6" t="n">
-        <v>105838</v>
+        <v>105897</v>
       </c>
       <c r="F92" s="6" t="n">
         <v>190166</v>
@@ -32003,7 +32003,7 @@
         <v>50701</v>
       </c>
       <c r="J92" s="6" t="n">
-        <v>54582</v>
+        <v>54600</v>
       </c>
     </row>
   </sheetData>
@@ -35419,7 +35419,7 @@
         <v>56040</v>
       </c>
       <c r="K91" t="n">
-        <v>88</v>
+        <v>99</v>
       </c>
     </row>
     <row r="92">
@@ -38857,7 +38857,7 @@
         <v>52540</v>
       </c>
       <c r="K91" t="n">
-        <v>133</v>
+        <v>137</v>
       </c>
     </row>
     <row r="92">

--- a/estado/registroRegional.xlsx
+++ b/estado/registroRegional.xlsx
@@ -7477,7 +7477,7 @@
         <v>0.001218784331953013</v>
       </c>
       <c r="E80" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F80" t="n">
         <v>467119</v>
@@ -7514,7 +7514,7 @@
         <v>0</v>
       </c>
       <c r="E81" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F81" t="n">
         <v>470002</v>
@@ -7899,10 +7899,10 @@
         <v>-0.001921826723947268</v>
       </c>
       <c r="J91" t="n">
-        <v>69005</v>
+        <v>69056</v>
       </c>
       <c r="K91" t="n">
-        <v>201</v>
+        <v>185</v>
       </c>
     </row>
     <row r="92">
@@ -7924,7 +7924,7 @@
         <v>28740</v>
       </c>
       <c r="J92" s="6" t="n">
-        <v>69005</v>
+        <v>69056</v>
       </c>
     </row>
   </sheetData>
@@ -11322,7 +11322,7 @@
         <v>-1.223439596904886e-05</v>
       </c>
       <c r="E91" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F91" t="n">
         <v>756019</v>
@@ -11340,7 +11340,7 @@
         <v>79013</v>
       </c>
       <c r="K91" t="n">
-        <v>456</v>
+        <v>472</v>
       </c>
     </row>
     <row r="92">
@@ -14773,25 +14773,25 @@
         <v>0.001947722580782786</v>
       </c>
       <c r="E91" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F91" t="n">
-        <v>1159049</v>
+        <v>1160076</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
       </c>
       <c r="H91" t="n">
-        <v>109913</v>
+        <v>112225</v>
       </c>
       <c r="I91" s="5" t="n">
-        <v>0</v>
+        <v>0.002631284467147164</v>
       </c>
       <c r="J91" t="n">
-        <v>139793</v>
+        <v>139821</v>
       </c>
       <c r="K91" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="92">
@@ -14804,16 +14804,16 @@
         <v>483548</v>
       </c>
       <c r="F92" s="6" t="n">
-        <v>616453</v>
+        <v>617480</v>
       </c>
       <c r="G92" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H92" s="6" t="n">
-        <v>109913</v>
+        <v>112225</v>
       </c>
       <c r="J92" s="6" t="n">
-        <v>139793</v>
+        <v>139821</v>
       </c>
     </row>
   </sheetData>
@@ -18202,16 +18202,16 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>1208589</v>
+        <v>1209364</v>
       </c>
       <c r="C91" t="n">
         <v>0</v>
       </c>
       <c r="D91" s="5" t="n">
-        <v>-0.0001274050811462817</v>
+        <v>0.0005137568531937723</v>
       </c>
       <c r="E91" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F91" t="n">
         <v>530625</v>
@@ -18229,7 +18229,7 @@
         <v>78979</v>
       </c>
       <c r="K91" t="n">
-        <v>306</v>
+        <v>319</v>
       </c>
     </row>
     <row r="92">
@@ -18239,7 +18239,7 @@
         </is>
       </c>
       <c r="B92" s="6" t="n">
-        <v>78526</v>
+        <v>79301</v>
       </c>
       <c r="F92" s="6" t="n">
         <v>295768</v>
@@ -21649,7 +21649,7 @@
         <v>0.0005241552487540086</v>
       </c>
       <c r="E91" t="n">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="F91" t="n">
         <v>1840346</v>
@@ -21664,10 +21664,10 @@
         <v>0.002021536922692947</v>
       </c>
       <c r="J91" t="n">
-        <v>188265</v>
+        <v>188432</v>
       </c>
       <c r="K91" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="92">
@@ -21689,7 +21689,7 @@
         <v>131855</v>
       </c>
       <c r="J92" s="6" t="n">
-        <v>188265</v>
+        <v>188432</v>
       </c>
     </row>
   </sheetData>
@@ -25087,7 +25087,7 @@
         <v>0</v>
       </c>
       <c r="E91" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F91" t="n">
         <v>590365</v>
@@ -25102,10 +25102,10 @@
         <v>0</v>
       </c>
       <c r="J91" t="n">
-        <v>60875</v>
+        <v>60873</v>
       </c>
       <c r="K91" t="n">
-        <v>4</v>
+        <v>27</v>
       </c>
     </row>
     <row r="92">
@@ -25127,7 +25127,7 @@
         <v>76288</v>
       </c>
       <c r="J92" s="6" t="n">
-        <v>60875</v>
+        <v>60873</v>
       </c>
     </row>
   </sheetData>
@@ -28516,16 +28516,16 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>934221</v>
+        <v>935365</v>
       </c>
       <c r="C91" t="n">
         <v>11614</v>
       </c>
       <c r="D91" s="5" t="n">
-        <v>-1.162980020003256e-05</v>
+        <v>0.001197869420603354</v>
       </c>
       <c r="E91" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F91" t="n">
         <v>500298</v>
@@ -28540,10 +28540,10 @@
         <v>0.00301908206515415</v>
       </c>
       <c r="J91" t="n">
-        <v>65708</v>
+        <v>65835</v>
       </c>
       <c r="K91" t="n">
-        <v>325</v>
+        <v>204</v>
       </c>
     </row>
     <row r="92">
@@ -28553,7 +28553,7 @@
         </is>
       </c>
       <c r="B92" s="6" t="n">
-        <v>91740</v>
+        <v>92884</v>
       </c>
       <c r="F92" s="6" t="n">
         <v>225386</v>
@@ -28565,7 +28565,7 @@
         <v>122284</v>
       </c>
       <c r="J92" s="6" t="n">
-        <v>65708</v>
+        <v>65835</v>
       </c>
     </row>
   </sheetData>
@@ -31954,16 +31954,16 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>799733</v>
+        <v>799807</v>
       </c>
       <c r="C91" t="n">
         <v>0</v>
       </c>
       <c r="D91" s="5" t="n">
-        <v>7.378006537664098e-05</v>
+        <v>0.0001663177744931059</v>
       </c>
       <c r="E91" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F91" t="n">
         <v>296573</v>
@@ -31978,7 +31978,7 @@
         <v>-0.0003798681397108973</v>
       </c>
       <c r="J91" t="n">
-        <v>54600</v>
+        <v>54609</v>
       </c>
       <c r="K91" t="n">
         <v>0</v>
@@ -31991,7 +31991,7 @@
         </is>
       </c>
       <c r="B92" s="6" t="n">
-        <v>105897</v>
+        <v>105971</v>
       </c>
       <c r="F92" s="6" t="n">
         <v>190166</v>
@@ -32003,7 +32003,7 @@
         <v>50701</v>
       </c>
       <c r="J92" s="6" t="n">
-        <v>54600</v>
+        <v>54609</v>
       </c>
     </row>
   </sheetData>
@@ -35419,7 +35419,7 @@
         <v>56040</v>
       </c>
       <c r="K91" t="n">
-        <v>99</v>
+        <v>110</v>
       </c>
     </row>
     <row r="92">
@@ -38857,7 +38857,7 @@
         <v>52540</v>
       </c>
       <c r="K91" t="n">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="92">

--- a/estado/registroRegional.xlsx
+++ b/estado/registroRegional.xlsx
@@ -7902,7 +7902,7 @@
         <v>69056</v>
       </c>
       <c r="K91" t="n">
-        <v>185</v>
+        <v>208</v>
       </c>
     </row>
     <row r="92">
@@ -11322,7 +11322,7 @@
         <v>-1.223439596904886e-05</v>
       </c>
       <c r="E91" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F91" t="n">
         <v>756019</v>
@@ -11340,7 +11340,7 @@
         <v>79013</v>
       </c>
       <c r="K91" t="n">
-        <v>472</v>
+        <v>516</v>
       </c>
     </row>
     <row r="92">
@@ -14773,7 +14773,7 @@
         <v>0.001947722580782786</v>
       </c>
       <c r="E91" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F91" t="n">
         <v>1160076</v>
@@ -14788,10 +14788,10 @@
         <v>0.002631284467147164</v>
       </c>
       <c r="J91" t="n">
-        <v>139821</v>
+        <v>139869</v>
       </c>
       <c r="K91" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="92">
@@ -14813,7 +14813,7 @@
         <v>112225</v>
       </c>
       <c r="J92" s="6" t="n">
-        <v>139821</v>
+        <v>139869</v>
       </c>
     </row>
   </sheetData>
@@ -18202,16 +18202,16 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>1209364</v>
+        <v>1211779</v>
       </c>
       <c r="C91" t="n">
         <v>0</v>
       </c>
       <c r="D91" s="5" t="n">
-        <v>0.0005137568531937723</v>
+        <v>0.002511700171169554</v>
       </c>
       <c r="E91" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F91" t="n">
         <v>530625</v>
@@ -18229,7 +18229,7 @@
         <v>78979</v>
       </c>
       <c r="K91" t="n">
-        <v>319</v>
+        <v>325</v>
       </c>
     </row>
     <row r="92">
@@ -18239,7 +18239,7 @@
         </is>
       </c>
       <c r="B92" s="6" t="n">
-        <v>79301</v>
+        <v>81716</v>
       </c>
       <c r="F92" s="6" t="n">
         <v>295768</v>
@@ -21649,7 +21649,7 @@
         <v>0.0005241552487540086</v>
       </c>
       <c r="E91" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F91" t="n">
         <v>1840346</v>
@@ -21667,7 +21667,7 @@
         <v>188432</v>
       </c>
       <c r="K91" t="n">
-        <v>13</v>
+        <v>32</v>
       </c>
     </row>
     <row r="92">
@@ -25102,10 +25102,10 @@
         <v>0</v>
       </c>
       <c r="J91" t="n">
-        <v>60873</v>
+        <v>60898</v>
       </c>
       <c r="K91" t="n">
-        <v>27</v>
+        <v>8</v>
       </c>
     </row>
     <row r="92">
@@ -25127,7 +25127,7 @@
         <v>76288</v>
       </c>
       <c r="J92" s="6" t="n">
-        <v>60873</v>
+        <v>60898</v>
       </c>
     </row>
   </sheetData>
@@ -28540,10 +28540,10 @@
         <v>0.00301908206515415</v>
       </c>
       <c r="J91" t="n">
-        <v>65835</v>
+        <v>65904</v>
       </c>
       <c r="K91" t="n">
-        <v>204</v>
+        <v>141</v>
       </c>
     </row>
     <row r="92">
@@ -28565,7 +28565,7 @@
         <v>122284</v>
       </c>
       <c r="J92" s="6" t="n">
-        <v>65835</v>
+        <v>65904</v>
       </c>
     </row>
   </sheetData>
@@ -31954,16 +31954,16 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>799807</v>
+        <v>801243</v>
       </c>
       <c r="C91" t="n">
         <v>0</v>
       </c>
       <c r="D91" s="5" t="n">
-        <v>0.0001663177744931059</v>
+        <v>0.001962049535185588</v>
       </c>
       <c r="E91" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F91" t="n">
         <v>296573</v>
@@ -31978,7 +31978,7 @@
         <v>-0.0003798681397108973</v>
       </c>
       <c r="J91" t="n">
-        <v>54609</v>
+        <v>54620</v>
       </c>
       <c r="K91" t="n">
         <v>0</v>
@@ -31991,7 +31991,7 @@
         </is>
       </c>
       <c r="B92" s="6" t="n">
-        <v>105971</v>
+        <v>107407</v>
       </c>
       <c r="F92" s="6" t="n">
         <v>190166</v>
@@ -32003,7 +32003,7 @@
         <v>50701</v>
       </c>
       <c r="J92" s="6" t="n">
-        <v>54609</v>
+        <v>54620</v>
       </c>
     </row>
   </sheetData>
@@ -35419,7 +35419,7 @@
         <v>56040</v>
       </c>
       <c r="K91" t="n">
-        <v>110</v>
+        <v>137</v>
       </c>
     </row>
     <row r="92">

--- a/estado/registroRegional.xlsx
+++ b/estado/registroRegional.xlsx
@@ -7902,7 +7902,7 @@
         <v>69056</v>
       </c>
       <c r="K91" t="n">
-        <v>208</v>
+        <v>229</v>
       </c>
     </row>
     <row r="92">
@@ -11340,7 +11340,7 @@
         <v>79013</v>
       </c>
       <c r="K91" t="n">
-        <v>516</v>
+        <v>526</v>
       </c>
     </row>
     <row r="92">
@@ -14773,7 +14773,7 @@
         <v>0.001947722580782786</v>
       </c>
       <c r="E91" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F91" t="n">
         <v>1160076</v>
@@ -14791,7 +14791,7 @@
         <v>139869</v>
       </c>
       <c r="K91" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
     </row>
     <row r="92">
@@ -18229,7 +18229,7 @@
         <v>78979</v>
       </c>
       <c r="K91" t="n">
-        <v>325</v>
+        <v>337</v>
       </c>
     </row>
     <row r="92">
@@ -21649,7 +21649,7 @@
         <v>0.0005241552487540086</v>
       </c>
       <c r="E91" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F91" t="n">
         <v>1840346</v>
@@ -21667,7 +21667,7 @@
         <v>188432</v>
       </c>
       <c r="K91" t="n">
-        <v>32</v>
+        <v>55</v>
       </c>
     </row>
     <row r="92">
@@ -25105,7 +25105,7 @@
         <v>60898</v>
       </c>
       <c r="K91" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="92">
@@ -28543,7 +28543,7 @@
         <v>65904</v>
       </c>
       <c r="K91" t="n">
-        <v>141</v>
+        <v>158</v>
       </c>
     </row>
     <row r="92">
@@ -31981,7 +31981,7 @@
         <v>54620</v>
       </c>
       <c r="K91" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="92">
@@ -35401,7 +35401,7 @@
         <v>0.0001098859865885494</v>
       </c>
       <c r="E91" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F91" t="n">
         <v>348031</v>
@@ -35419,7 +35419,7 @@
         <v>56040</v>
       </c>
       <c r="K91" t="n">
-        <v>137</v>
+        <v>143</v>
       </c>
     </row>
     <row r="92">
@@ -38857,7 +38857,7 @@
         <v>52540</v>
       </c>
       <c r="K91" t="n">
-        <v>139</v>
+        <v>151</v>
       </c>
     </row>
     <row r="92">

--- a/estado/registroRegional.xlsx
+++ b/estado/registroRegional.xlsx
@@ -7902,7 +7902,7 @@
         <v>69056</v>
       </c>
       <c r="K91" t="n">
-        <v>229</v>
+        <v>240</v>
       </c>
     </row>
     <row r="92">
@@ -11340,7 +11340,7 @@
         <v>79013</v>
       </c>
       <c r="K91" t="n">
-        <v>526</v>
+        <v>544</v>
       </c>
     </row>
     <row r="92">
@@ -14773,7 +14773,7 @@
         <v>0.001947722580782786</v>
       </c>
       <c r="E91" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F91" t="n">
         <v>1160076</v>
@@ -14791,7 +14791,7 @@
         <v>139869</v>
       </c>
       <c r="K91" t="n">
-        <v>25</v>
+        <v>44</v>
       </c>
     </row>
     <row r="92">
@@ -18229,7 +18229,7 @@
         <v>78979</v>
       </c>
       <c r="K91" t="n">
-        <v>337</v>
+        <v>346</v>
       </c>
     </row>
     <row r="92">
@@ -21649,7 +21649,7 @@
         <v>0.0005241552487540086</v>
       </c>
       <c r="E91" t="n">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="F91" t="n">
         <v>1840346</v>
@@ -21667,7 +21667,7 @@
         <v>188432</v>
       </c>
       <c r="K91" t="n">
-        <v>55</v>
+        <v>87</v>
       </c>
     </row>
     <row r="92">
@@ -25105,7 +25105,7 @@
         <v>60898</v>
       </c>
       <c r="K91" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
     </row>
     <row r="92">
@@ -28543,7 +28543,7 @@
         <v>65904</v>
       </c>
       <c r="K91" t="n">
-        <v>158</v>
+        <v>177</v>
       </c>
     </row>
     <row r="92">
@@ -31981,7 +31981,7 @@
         <v>54620</v>
       </c>
       <c r="K91" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="92">
@@ -35419,7 +35419,7 @@
         <v>56040</v>
       </c>
       <c r="K91" t="n">
-        <v>143</v>
+        <v>163</v>
       </c>
     </row>
     <row r="92">
@@ -38857,7 +38857,7 @@
         <v>52540</v>
       </c>
       <c r="K91" t="n">
-        <v>151</v>
+        <v>156</v>
       </c>
     </row>
     <row r="92">

--- a/estado/registroRegional.xlsx
+++ b/estado/registroRegional.xlsx
@@ -7899,10 +7899,10 @@
         <v>-0.001921826723947268</v>
       </c>
       <c r="J91" t="n">
-        <v>69056</v>
+        <v>69054</v>
       </c>
       <c r="K91" t="n">
-        <v>240</v>
+        <v>252</v>
       </c>
     </row>
     <row r="92">
@@ -7924,7 +7924,7 @@
         <v>28740</v>
       </c>
       <c r="J92" s="6" t="n">
-        <v>69056</v>
+        <v>69054</v>
       </c>
     </row>
   </sheetData>
@@ -11322,7 +11322,7 @@
         <v>-1.223439596904886e-05</v>
       </c>
       <c r="E91" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F91" t="n">
         <v>756019</v>
@@ -11340,7 +11340,7 @@
         <v>79013</v>
       </c>
       <c r="K91" t="n">
-        <v>544</v>
+        <v>557</v>
       </c>
     </row>
     <row r="92">
@@ -14773,7 +14773,7 @@
         <v>0.001947722580782786</v>
       </c>
       <c r="E91" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F91" t="n">
         <v>1160076</v>
@@ -14788,10 +14788,10 @@
         <v>0.002631284467147164</v>
       </c>
       <c r="J91" t="n">
-        <v>139869</v>
+        <v>139903</v>
       </c>
       <c r="K91" t="n">
-        <v>44</v>
+        <v>63</v>
       </c>
     </row>
     <row r="92">
@@ -14813,7 +14813,7 @@
         <v>112225</v>
       </c>
       <c r="J92" s="6" t="n">
-        <v>139869</v>
+        <v>139903</v>
       </c>
     </row>
   </sheetData>
@@ -18202,13 +18202,13 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>1211779</v>
+        <v>1211690</v>
       </c>
       <c r="C91" t="n">
         <v>0</v>
       </c>
       <c r="D91" s="5" t="n">
-        <v>0.002511700171169554</v>
+        <v>0.002438069961935664</v>
       </c>
       <c r="E91" t="n">
         <v>7</v>
@@ -18229,7 +18229,7 @@
         <v>78979</v>
       </c>
       <c r="K91" t="n">
-        <v>346</v>
+        <v>352</v>
       </c>
     </row>
     <row r="92">
@@ -18239,7 +18239,7 @@
         </is>
       </c>
       <c r="B92" s="6" t="n">
-        <v>81716</v>
+        <v>81627</v>
       </c>
       <c r="F92" s="6" t="n">
         <v>295768</v>
@@ -21649,7 +21649,7 @@
         <v>0.0005241552487540086</v>
       </c>
       <c r="E91" t="n">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="F91" t="n">
         <v>1840346</v>
@@ -21658,16 +21658,16 @@
         <v>123505</v>
       </c>
       <c r="H91" t="n">
-        <v>131855</v>
+        <v>133189</v>
       </c>
       <c r="I91" s="5" t="n">
-        <v>0.002021536922692947</v>
+        <v>0.002659363378433816</v>
       </c>
       <c r="J91" t="n">
-        <v>188432</v>
+        <v>188514</v>
       </c>
       <c r="K91" t="n">
-        <v>87</v>
+        <v>34</v>
       </c>
     </row>
     <row r="92">
@@ -21686,10 +21686,10 @@
         <v>123505</v>
       </c>
       <c r="H92" s="6" t="n">
-        <v>131855</v>
+        <v>133189</v>
       </c>
       <c r="J92" s="6" t="n">
-        <v>188432</v>
+        <v>188514</v>
       </c>
     </row>
   </sheetData>
@@ -25087,7 +25087,7 @@
         <v>0</v>
       </c>
       <c r="E91" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F91" t="n">
         <v>590365</v>
@@ -25102,10 +25102,10 @@
         <v>0</v>
       </c>
       <c r="J91" t="n">
-        <v>60898</v>
+        <v>60896</v>
       </c>
       <c r="K91" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="92">
@@ -25127,7 +25127,7 @@
         <v>76288</v>
       </c>
       <c r="J92" s="6" t="n">
-        <v>60898</v>
+        <v>60896</v>
       </c>
     </row>
   </sheetData>
@@ -28525,7 +28525,7 @@
         <v>0.001197869420603354</v>
       </c>
       <c r="E91" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F91" t="n">
         <v>500298</v>
@@ -28540,10 +28540,10 @@
         <v>0.00301908206515415</v>
       </c>
       <c r="J91" t="n">
-        <v>65904</v>
+        <v>65964</v>
       </c>
       <c r="K91" t="n">
-        <v>177</v>
+        <v>131</v>
       </c>
     </row>
     <row r="92">
@@ -28565,7 +28565,7 @@
         <v>122284</v>
       </c>
       <c r="J92" s="6" t="n">
-        <v>65904</v>
+        <v>65964</v>
       </c>
     </row>
   </sheetData>
@@ -31978,10 +31978,10 @@
         <v>-0.0003798681397108973</v>
       </c>
       <c r="J91" t="n">
-        <v>54620</v>
+        <v>54638</v>
       </c>
       <c r="K91" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
@@ -32003,7 +32003,7 @@
         <v>50701</v>
       </c>
       <c r="J92" s="6" t="n">
-        <v>54620</v>
+        <v>54638</v>
       </c>
     </row>
   </sheetData>
@@ -35419,7 +35419,7 @@
         <v>56040</v>
       </c>
       <c r="K91" t="n">
-        <v>163</v>
+        <v>183</v>
       </c>
     </row>
     <row r="92">
@@ -38854,10 +38854,10 @@
         <v>0</v>
       </c>
       <c r="J91" t="n">
-        <v>52540</v>
+        <v>52543</v>
       </c>
       <c r="K91" t="n">
-        <v>156</v>
+        <v>161</v>
       </c>
     </row>
     <row r="92">
@@ -38879,7 +38879,7 @@
         <v>72</v>
       </c>
       <c r="J92" s="6" t="n">
-        <v>52540</v>
+        <v>52543</v>
       </c>
     </row>
   </sheetData>

--- a/estado/registroRegional.xlsx
+++ b/estado/registroRegional.xlsx
@@ -7899,10 +7899,10 @@
         <v>-0.001921826723947268</v>
       </c>
       <c r="J91" t="n">
-        <v>69054</v>
+        <v>69092</v>
       </c>
       <c r="K91" t="n">
-        <v>252</v>
+        <v>220</v>
       </c>
     </row>
     <row r="92">
@@ -7924,7 +7924,7 @@
         <v>28740</v>
       </c>
       <c r="J92" s="6" t="n">
-        <v>69054</v>
+        <v>69092</v>
       </c>
     </row>
   </sheetData>
@@ -11322,7 +11322,7 @@
         <v>-1.223439596904886e-05</v>
       </c>
       <c r="E91" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F91" t="n">
         <v>756019</v>
@@ -11340,7 +11340,7 @@
         <v>79013</v>
       </c>
       <c r="K91" t="n">
-        <v>557</v>
+        <v>578</v>
       </c>
     </row>
     <row r="92">
@@ -14773,7 +14773,7 @@
         <v>0.001947722580782786</v>
       </c>
       <c r="E91" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F91" t="n">
         <v>1160076</v>
@@ -14788,10 +14788,10 @@
         <v>0.002631284467147164</v>
       </c>
       <c r="J91" t="n">
-        <v>139903</v>
+        <v>139991</v>
       </c>
       <c r="K91" t="n">
-        <v>63</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92">
@@ -14813,7 +14813,7 @@
         <v>112225</v>
       </c>
       <c r="J92" s="6" t="n">
-        <v>139903</v>
+        <v>139991</v>
       </c>
     </row>
   </sheetData>
@@ -18229,7 +18229,7 @@
         <v>78979</v>
       </c>
       <c r="K91" t="n">
-        <v>352</v>
+        <v>361</v>
       </c>
     </row>
     <row r="92">
@@ -21649,7 +21649,7 @@
         <v>0.0005241552487540086</v>
       </c>
       <c r="E91" t="n">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="F91" t="n">
         <v>1840346</v>
@@ -21667,7 +21667,7 @@
         <v>188514</v>
       </c>
       <c r="K91" t="n">
-        <v>34</v>
+        <v>55</v>
       </c>
     </row>
     <row r="92">
@@ -25087,7 +25087,7 @@
         <v>0</v>
       </c>
       <c r="E91" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F91" t="n">
         <v>590365</v>
@@ -25105,7 +25105,7 @@
         <v>60896</v>
       </c>
       <c r="K91" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
     </row>
     <row r="92">
@@ -28540,10 +28540,10 @@
         <v>0.00301908206515415</v>
       </c>
       <c r="J91" t="n">
-        <v>65964</v>
+        <v>65972</v>
       </c>
       <c r="K91" t="n">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="92">
@@ -28565,7 +28565,7 @@
         <v>122284</v>
       </c>
       <c r="J92" s="6" t="n">
-        <v>65964</v>
+        <v>65972</v>
       </c>
     </row>
   </sheetData>
@@ -31963,7 +31963,7 @@
         <v>0.001962049535185588</v>
       </c>
       <c r="E91" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F91" t="n">
         <v>296573</v>
@@ -31978,7 +31978,7 @@
         <v>-0.0003798681397108973</v>
       </c>
       <c r="J91" t="n">
-        <v>54638</v>
+        <v>54643</v>
       </c>
       <c r="K91" t="n">
         <v>0</v>
@@ -32003,7 +32003,7 @@
         <v>50701</v>
       </c>
       <c r="J92" s="6" t="n">
-        <v>54638</v>
+        <v>54643</v>
       </c>
     </row>
   </sheetData>
@@ -35419,7 +35419,7 @@
         <v>56040</v>
       </c>
       <c r="K91" t="n">
-        <v>183</v>
+        <v>194</v>
       </c>
     </row>
     <row r="92">
@@ -38857,7 +38857,7 @@
         <v>52543</v>
       </c>
       <c r="K91" t="n">
-        <v>161</v>
+        <v>172</v>
       </c>
     </row>
     <row r="92">

--- a/estado/registroRegional.xlsx
+++ b/estado/registroRegional.xlsx
@@ -7899,10 +7899,10 @@
         <v>-0.001921826723947268</v>
       </c>
       <c r="J91" t="n">
-        <v>69092</v>
+        <v>69093</v>
       </c>
       <c r="K91" t="n">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="92">
@@ -7924,7 +7924,7 @@
         <v>28740</v>
       </c>
       <c r="J92" s="6" t="n">
-        <v>69092</v>
+        <v>69093</v>
       </c>
     </row>
   </sheetData>
@@ -11322,7 +11322,7 @@
         <v>-1.223439596904886e-05</v>
       </c>
       <c r="E91" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F91" t="n">
         <v>756019</v>
@@ -14773,7 +14773,7 @@
         <v>0.001947722580782786</v>
       </c>
       <c r="E91" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F91" t="n">
         <v>1160076</v>
@@ -18202,16 +18202,16 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>1211690</v>
+        <v>1213564</v>
       </c>
       <c r="C91" t="n">
         <v>0</v>
       </c>
       <c r="D91" s="5" t="n">
-        <v>0.002438069961935664</v>
+        <v>0.003988440884456001</v>
       </c>
       <c r="E91" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F91" t="n">
         <v>530625</v>
@@ -18239,7 +18239,7 @@
         </is>
       </c>
       <c r="B92" s="6" t="n">
-        <v>81627</v>
+        <v>83501</v>
       </c>
       <c r="F92" s="6" t="n">
         <v>295768</v>
@@ -19207,7 +19207,7 @@
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F25" t="n">
         <v>1582242</v>
@@ -21649,7 +21649,7 @@
         <v>0.0005241552487540086</v>
       </c>
       <c r="E91" t="n">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="F91" t="n">
         <v>1840346</v>
@@ -25102,10 +25102,10 @@
         <v>0</v>
       </c>
       <c r="J91" t="n">
-        <v>60896</v>
+        <v>60929</v>
       </c>
       <c r="K91" t="n">
-        <v>38</v>
+        <v>5</v>
       </c>
     </row>
     <row r="92">
@@ -25127,7 +25127,7 @@
         <v>76288</v>
       </c>
       <c r="J92" s="6" t="n">
-        <v>60896</v>
+        <v>60929</v>
       </c>
     </row>
   </sheetData>
@@ -28516,13 +28516,13 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>935365</v>
+        <v>935351</v>
       </c>
       <c r="C91" t="n">
         <v>11614</v>
       </c>
       <c r="D91" s="5" t="n">
-        <v>0.001197869420603354</v>
+        <v>0.001183067856712404</v>
       </c>
       <c r="E91" t="n">
         <v>6</v>
@@ -28540,10 +28540,10 @@
         <v>0.00301908206515415</v>
       </c>
       <c r="J91" t="n">
-        <v>65972</v>
+        <v>65974</v>
       </c>
       <c r="K91" t="n">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="92">
@@ -28553,7 +28553,7 @@
         </is>
       </c>
       <c r="B92" s="6" t="n">
-        <v>92884</v>
+        <v>92870</v>
       </c>
       <c r="F92" s="6" t="n">
         <v>225386</v>
@@ -28565,7 +28565,7 @@
         <v>122284</v>
       </c>
       <c r="J92" s="6" t="n">
-        <v>65972</v>
+        <v>65974</v>
       </c>
     </row>
   </sheetData>
@@ -31978,7 +31978,7 @@
         <v>-0.0003798681397108973</v>
       </c>
       <c r="J91" t="n">
-        <v>54643</v>
+        <v>54641</v>
       </c>
       <c r="K91" t="n">
         <v>0</v>
@@ -32003,7 +32003,7 @@
         <v>50701</v>
       </c>
       <c r="J92" s="6" t="n">
-        <v>54643</v>
+        <v>54641</v>
       </c>
     </row>
   </sheetData>
@@ -35401,7 +35401,7 @@
         <v>0.0001098859865885494</v>
       </c>
       <c r="E91" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F91" t="n">
         <v>348031</v>

--- a/estado/registroRegional.xlsx
+++ b/estado/registroRegional.xlsx
@@ -7884,25 +7884,25 @@
         <v>-4.633846675281208e-05</v>
       </c>
       <c r="E91" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F91" t="n">
-        <v>562497</v>
+        <v>515663</v>
       </c>
       <c r="G91" t="n">
-        <v>4444</v>
+        <v>50527</v>
       </c>
       <c r="H91" t="n">
-        <v>28740</v>
+        <v>28993</v>
       </c>
       <c r="I91" s="5" t="n">
-        <v>-0.001921826723947268</v>
+        <v>-0.002756237978110946</v>
       </c>
       <c r="J91" t="n">
         <v>69093</v>
       </c>
       <c r="K91" t="n">
-        <v>219</v>
+        <v>356</v>
       </c>
     </row>
     <row r="92">
@@ -7915,13 +7915,13 @@
         <v>133520</v>
       </c>
       <c r="F92" s="6" t="n">
-        <v>341836</v>
+        <v>295002</v>
       </c>
       <c r="G92" s="6" t="n">
-        <v>4444</v>
+        <v>50527</v>
       </c>
       <c r="H92" s="6" t="n">
-        <v>28740</v>
+        <v>28993</v>
       </c>
       <c r="J92" s="6" t="n">
         <v>69093</v>
@@ -11322,25 +11322,25 @@
         <v>-1.223439596904886e-05</v>
       </c>
       <c r="E91" t="n">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="F91" t="n">
-        <v>756019</v>
+        <v>750284</v>
       </c>
       <c r="G91" t="n">
         <v>26677</v>
       </c>
       <c r="H91" t="n">
-        <v>91062</v>
+        <v>94817</v>
       </c>
       <c r="I91" s="5" t="n">
-        <v>0</v>
+        <v>-0.002266073672572955</v>
       </c>
       <c r="J91" t="n">
         <v>79013</v>
       </c>
       <c r="K91" t="n">
-        <v>578</v>
+        <v>677</v>
       </c>
     </row>
     <row r="92">
@@ -11353,13 +11353,13 @@
         <v>213139</v>
       </c>
       <c r="F92" s="6" t="n">
-        <v>257112</v>
+        <v>251377</v>
       </c>
       <c r="G92" s="6" t="n">
         <v>26677</v>
       </c>
       <c r="H92" s="6" t="n">
-        <v>91062</v>
+        <v>94817</v>
       </c>
       <c r="J92" s="6" t="n">
         <v>79013</v>
@@ -14764,34 +14764,34 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>1690899</v>
+        <v>1699553</v>
       </c>
       <c r="C91" t="n">
         <v>0</v>
       </c>
       <c r="D91" s="5" t="n">
-        <v>0.001947722580782786</v>
+        <v>0.007075678532743308</v>
       </c>
       <c r="E91" t="n">
+        <v>45</v>
+      </c>
+      <c r="F91" t="n">
+        <v>1158707</v>
+      </c>
+      <c r="G91" t="n">
+        <v>0</v>
+      </c>
+      <c r="H91" t="n">
+        <v>115237</v>
+      </c>
+      <c r="I91" s="5" t="n">
+        <v>0.003926043490664023</v>
+      </c>
+      <c r="J91" t="n">
+        <v>140208</v>
+      </c>
+      <c r="K91" t="n">
         <v>28</v>
-      </c>
-      <c r="F91" t="n">
-        <v>1160076</v>
-      </c>
-      <c r="G91" t="n">
-        <v>0</v>
-      </c>
-      <c r="H91" t="n">
-        <v>112225</v>
-      </c>
-      <c r="I91" s="5" t="n">
-        <v>0.002631284467147164</v>
-      </c>
-      <c r="J91" t="n">
-        <v>139991</v>
-      </c>
-      <c r="K91" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="92">
@@ -14801,19 +14801,19 @@
         </is>
       </c>
       <c r="B92" s="6" t="n">
-        <v>483548</v>
+        <v>492202</v>
       </c>
       <c r="F92" s="6" t="n">
-        <v>617480</v>
+        <v>616111</v>
       </c>
       <c r="G92" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H92" s="6" t="n">
-        <v>112225</v>
+        <v>115237</v>
       </c>
       <c r="J92" s="6" t="n">
-        <v>139991</v>
+        <v>140208</v>
       </c>
     </row>
   </sheetData>
@@ -18211,7 +18211,7 @@
         <v>0.003988440884456001</v>
       </c>
       <c r="E91" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="F91" t="n">
         <v>530625</v>
@@ -18220,16 +18220,16 @@
         <v>0</v>
       </c>
       <c r="H91" t="n">
-        <v>122921</v>
+        <v>124152</v>
       </c>
       <c r="I91" s="5" t="n">
-        <v>0.001844121880667072</v>
+        <v>0.003731165966370452</v>
       </c>
       <c r="J91" t="n">
-        <v>78979</v>
+        <v>79203</v>
       </c>
       <c r="K91" t="n">
-        <v>361</v>
+        <v>262</v>
       </c>
     </row>
     <row r="92">
@@ -18248,10 +18248,10 @@
         <v>0</v>
       </c>
       <c r="H92" s="6" t="n">
-        <v>122921</v>
+        <v>124152</v>
       </c>
       <c r="J92" s="6" t="n">
-        <v>78979</v>
+        <v>79203</v>
       </c>
     </row>
   </sheetData>
@@ -19207,7 +19207,7 @@
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F25" t="n">
         <v>1582242</v>
@@ -21640,34 +21640,34 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>3070048</v>
+        <v>3071738</v>
       </c>
       <c r="C91" t="n">
-        <v>48983</v>
+        <v>49144</v>
       </c>
       <c r="D91" s="5" t="n">
-        <v>0.0005241552487540086</v>
+        <v>0.00111791985428869</v>
       </c>
       <c r="E91" t="n">
-        <v>129</v>
+        <v>225</v>
       </c>
       <c r="F91" t="n">
-        <v>1840346</v>
+        <v>1840404</v>
       </c>
       <c r="G91" t="n">
         <v>123505</v>
       </c>
       <c r="H91" t="n">
-        <v>133189</v>
+        <v>134758</v>
       </c>
       <c r="I91" s="5" t="n">
-        <v>0.002659363378433816</v>
+        <v>0.003437282151664995</v>
       </c>
       <c r="J91" t="n">
-        <v>188514</v>
+        <v>188886</v>
       </c>
       <c r="K91" t="n">
-        <v>55</v>
+        <v>3</v>
       </c>
     </row>
     <row r="92">
@@ -21677,19 +21677,19 @@
         </is>
       </c>
       <c r="B92" s="6" t="n">
-        <v>734227</v>
+        <v>735917</v>
       </c>
       <c r="F92" s="6" t="n">
-        <v>955882</v>
+        <v>955940</v>
       </c>
       <c r="G92" s="6" t="n">
         <v>123505</v>
       </c>
       <c r="H92" s="6" t="n">
-        <v>133189</v>
+        <v>134758</v>
       </c>
       <c r="J92" s="6" t="n">
-        <v>188514</v>
+        <v>188886</v>
       </c>
     </row>
   </sheetData>
@@ -25078,16 +25078,16 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>946647</v>
+        <v>947475</v>
       </c>
       <c r="C91" t="n">
         <v>0</v>
       </c>
       <c r="D91" s="5" t="n">
-        <v>0</v>
+        <v>0.0008746660582033218</v>
       </c>
       <c r="E91" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F91" t="n">
         <v>590365</v>
@@ -25096,16 +25096,16 @@
         <v>4948</v>
       </c>
       <c r="H91" t="n">
-        <v>76288</v>
+        <v>78113</v>
       </c>
       <c r="I91" s="5" t="n">
-        <v>0</v>
+        <v>0.002717387258208371</v>
       </c>
       <c r="J91" t="n">
-        <v>60929</v>
+        <v>61115</v>
       </c>
       <c r="K91" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
@@ -25115,7 +25115,7 @@
         </is>
       </c>
       <c r="B92" s="6" t="n">
-        <v>217757</v>
+        <v>218585</v>
       </c>
       <c r="F92" s="6" t="n">
         <v>358194</v>
@@ -25124,10 +25124,10 @@
         <v>4948</v>
       </c>
       <c r="H92" s="6" t="n">
-        <v>76288</v>
+        <v>78113</v>
       </c>
       <c r="J92" s="6" t="n">
-        <v>60929</v>
+        <v>61115</v>
       </c>
     </row>
   </sheetData>
@@ -28525,25 +28525,25 @@
         <v>0.001183067856712404</v>
       </c>
       <c r="E91" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F91" t="n">
-        <v>500298</v>
+        <v>500352</v>
       </c>
       <c r="G91" t="n">
         <v>6655</v>
       </c>
       <c r="H91" t="n">
-        <v>122284</v>
+        <v>101039</v>
       </c>
       <c r="I91" s="5" t="n">
-        <v>0.00301908206515415</v>
+        <v>-0.03075988733436095</v>
       </c>
       <c r="J91" t="n">
-        <v>65974</v>
+        <v>66009</v>
       </c>
       <c r="K91" t="n">
-        <v>127</v>
+        <v>190</v>
       </c>
     </row>
     <row r="92">
@@ -28556,16 +28556,16 @@
         <v>92870</v>
       </c>
       <c r="F92" s="6" t="n">
-        <v>225386</v>
+        <v>225440</v>
       </c>
       <c r="G92" s="6" t="n">
         <v>6655</v>
       </c>
       <c r="H92" s="6" t="n">
-        <v>122284</v>
+        <v>101039</v>
       </c>
       <c r="J92" s="6" t="n">
-        <v>65974</v>
+        <v>66009</v>
       </c>
     </row>
   </sheetData>
@@ -31954,34 +31954,34 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>801243</v>
+        <v>801513</v>
       </c>
       <c r="C91" t="n">
         <v>0</v>
       </c>
       <c r="D91" s="5" t="n">
-        <v>0.001962049535185588</v>
+        <v>0.00229968712250242</v>
       </c>
       <c r="E91" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F91" t="n">
-        <v>296573</v>
+        <v>296309</v>
       </c>
       <c r="G91" t="n">
         <v>83</v>
       </c>
       <c r="H91" t="n">
-        <v>50701</v>
+        <v>50918</v>
       </c>
       <c r="I91" s="5" t="n">
-        <v>-0.0003798681397108973</v>
+        <v>-0.0005151242197594744</v>
       </c>
       <c r="J91" t="n">
-        <v>54641</v>
+        <v>54702</v>
       </c>
       <c r="K91" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="92">
@@ -31991,19 +31991,19 @@
         </is>
       </c>
       <c r="B92" s="6" t="n">
-        <v>107407</v>
+        <v>107677</v>
       </c>
       <c r="F92" s="6" t="n">
-        <v>190166</v>
+        <v>189902</v>
       </c>
       <c r="G92" s="6" t="n">
         <v>83</v>
       </c>
       <c r="H92" s="6" t="n">
-        <v>50701</v>
+        <v>50918</v>
       </c>
       <c r="J92" s="6" t="n">
-        <v>54641</v>
+        <v>54702</v>
       </c>
     </row>
   </sheetData>
@@ -35392,34 +35392,34 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>746310</v>
+        <v>746418</v>
       </c>
       <c r="C91" t="n">
         <v>0</v>
       </c>
       <c r="D91" s="5" t="n">
-        <v>0.0001098859865885494</v>
+        <v>0.0002546138713637119</v>
       </c>
       <c r="E91" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F91" t="n">
-        <v>348031</v>
+        <v>346409</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
       </c>
       <c r="H91" t="n">
-        <v>29391</v>
+        <v>29534</v>
       </c>
       <c r="I91" s="5" t="n">
-        <v>-7.418201086236587e-05</v>
+        <v>-0.003992581798913764</v>
       </c>
       <c r="J91" t="n">
-        <v>56040</v>
+        <v>56224</v>
       </c>
       <c r="K91" t="n">
-        <v>194</v>
+        <v>104</v>
       </c>
     </row>
     <row r="92">
@@ -35429,19 +35429,19 @@
         </is>
       </c>
       <c r="B92" s="6" t="n">
-        <v>255379</v>
+        <v>255487</v>
       </c>
       <c r="F92" s="6" t="n">
-        <v>266610</v>
+        <v>264988</v>
       </c>
       <c r="G92" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H92" s="6" t="n">
-        <v>29391</v>
+        <v>29534</v>
       </c>
       <c r="J92" s="6" t="n">
-        <v>56040</v>
+        <v>56224</v>
       </c>
     </row>
   </sheetData>
@@ -38839,7 +38839,7 @@
         <v>0</v>
       </c>
       <c r="E91" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F91" t="n">
         <v>295759</v>
@@ -38854,10 +38854,10 @@
         <v>0</v>
       </c>
       <c r="J91" t="n">
-        <v>52543</v>
+        <v>52711</v>
       </c>
       <c r="K91" t="n">
-        <v>172</v>
+        <v>48</v>
       </c>
     </row>
     <row r="92">
@@ -38879,7 +38879,7 @@
         <v>72</v>
       </c>
       <c r="J92" s="6" t="n">
-        <v>52543</v>
+        <v>52711</v>
       </c>
     </row>
   </sheetData>

--- a/estado/registroRegional.xlsx
+++ b/estado/registroRegional.xlsx
@@ -11322,7 +11322,7 @@
         <v>-1.223439596904886e-05</v>
       </c>
       <c r="E91" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="F91" t="n">
         <v>750284</v>
@@ -14773,7 +14773,7 @@
         <v>0.007075678532743308</v>
       </c>
       <c r="E91" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F91" t="n">
         <v>1158707</v>
@@ -18211,7 +18211,7 @@
         <v>0.003988440884456001</v>
       </c>
       <c r="E91" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F91" t="n">
         <v>530625</v>
@@ -21649,7 +21649,7 @@
         <v>0.00111791985428869</v>
       </c>
       <c r="E91" t="n">
-        <v>225</v>
+        <v>238</v>
       </c>
       <c r="F91" t="n">
         <v>1840404</v>
@@ -21664,10 +21664,10 @@
         <v>0.003437282151664995</v>
       </c>
       <c r="J91" t="n">
-        <v>188886</v>
+        <v>188889</v>
       </c>
       <c r="K91" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
@@ -21689,7 +21689,7 @@
         <v>134758</v>
       </c>
       <c r="J92" s="6" t="n">
-        <v>188886</v>
+        <v>188889</v>
       </c>
     </row>
   </sheetData>
@@ -28525,7 +28525,7 @@
         <v>0.001183067856712404</v>
       </c>
       <c r="E91" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F91" t="n">
         <v>500352</v>
@@ -31963,7 +31963,7 @@
         <v>0.00229968712250242</v>
       </c>
       <c r="E91" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F91" t="n">
         <v>296309</v>
@@ -31978,10 +31978,10 @@
         <v>-0.0005151242197594744</v>
       </c>
       <c r="J91" t="n">
-        <v>54702</v>
+        <v>54705</v>
       </c>
       <c r="K91" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="92">
@@ -32003,7 +32003,7 @@
         <v>50918</v>
       </c>
       <c r="J92" s="6" t="n">
-        <v>54702</v>
+        <v>54705</v>
       </c>
     </row>
   </sheetData>
@@ -35416,10 +35416,10 @@
         <v>-0.003992581798913764</v>
       </c>
       <c r="J91" t="n">
-        <v>56224</v>
+        <v>56275</v>
       </c>
       <c r="K91" t="n">
-        <v>104</v>
+        <v>54</v>
       </c>
     </row>
     <row r="92">
@@ -35441,7 +35441,7 @@
         <v>29534</v>
       </c>
       <c r="J92" s="6" t="n">
-        <v>56224</v>
+        <v>56275</v>
       </c>
     </row>
   </sheetData>
@@ -38854,10 +38854,10 @@
         <v>0</v>
       </c>
       <c r="J91" t="n">
-        <v>52711</v>
+        <v>52712</v>
       </c>
       <c r="K91" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="92">
@@ -38879,7 +38879,7 @@
         <v>72</v>
       </c>
       <c r="J92" s="6" t="n">
-        <v>52711</v>
+        <v>52712</v>
       </c>
     </row>
   </sheetData>

--- a/estado/registroRegional.xlsx
+++ b/estado/registroRegional.xlsx
@@ -7884,7 +7884,7 @@
         <v>-4.633846675281208e-05</v>
       </c>
       <c r="E91" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F91" t="n">
         <v>515663</v>
@@ -11322,7 +11322,7 @@
         <v>-1.223439596904886e-05</v>
       </c>
       <c r="E91" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="F91" t="n">
         <v>750284</v>
@@ -14788,10 +14788,10 @@
         <v>0.003926043490664023</v>
       </c>
       <c r="J91" t="n">
-        <v>140208</v>
+        <v>140236</v>
       </c>
       <c r="K91" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
@@ -14813,7 +14813,7 @@
         <v>115237</v>
       </c>
       <c r="J92" s="6" t="n">
-        <v>140208</v>
+        <v>140236</v>
       </c>
     </row>
   </sheetData>
@@ -18211,19 +18211,19 @@
         <v>0.003988440884456001</v>
       </c>
       <c r="E91" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F91" t="n">
-        <v>530625</v>
+        <v>527808</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
       </c>
       <c r="H91" t="n">
-        <v>124152</v>
+        <v>167506</v>
       </c>
       <c r="I91" s="5" t="n">
-        <v>0.003731165966370452</v>
+        <v>0.06587178830768477</v>
       </c>
       <c r="J91" t="n">
         <v>79203</v>
@@ -18242,13 +18242,13 @@
         <v>83501</v>
       </c>
       <c r="F92" s="6" t="n">
-        <v>295768</v>
+        <v>292951</v>
       </c>
       <c r="G92" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H92" s="6" t="n">
-        <v>124152</v>
+        <v>167506</v>
       </c>
       <c r="J92" s="6" t="n">
         <v>79203</v>
@@ -21649,7 +21649,7 @@
         <v>0.00111791985428869</v>
       </c>
       <c r="E91" t="n">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="F91" t="n">
         <v>1840404</v>
@@ -31963,7 +31963,7 @@
         <v>0.00229968712250242</v>
       </c>
       <c r="E91" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F91" t="n">
         <v>296309</v>
@@ -31978,10 +31978,10 @@
         <v>-0.0005151242197594744</v>
       </c>
       <c r="J91" t="n">
-        <v>54705</v>
+        <v>54706</v>
       </c>
       <c r="K91" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92">
@@ -32003,7 +32003,7 @@
         <v>50918</v>
       </c>
       <c r="J92" s="6" t="n">
-        <v>54705</v>
+        <v>54706</v>
       </c>
     </row>
   </sheetData>
@@ -35401,7 +35401,7 @@
         <v>0.0002546138713637119</v>
       </c>
       <c r="E91" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F91" t="n">
         <v>346409</v>
@@ -35416,10 +35416,10 @@
         <v>-0.003992581798913764</v>
       </c>
       <c r="J91" t="n">
-        <v>56275</v>
+        <v>56285</v>
       </c>
       <c r="K91" t="n">
-        <v>54</v>
+        <v>34</v>
       </c>
     </row>
     <row r="92">
@@ -35441,7 +35441,7 @@
         <v>29534</v>
       </c>
       <c r="J92" s="6" t="n">
-        <v>56275</v>
+        <v>56285</v>
       </c>
     </row>
   </sheetData>
@@ -38839,7 +38839,7 @@
         <v>0</v>
       </c>
       <c r="E91" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F91" t="n">
         <v>295759</v>

--- a/estado/registroRegional.xlsx
+++ b/estado/registroRegional.xlsx
@@ -7884,7 +7884,7 @@
         <v>-4.633846675281208e-05</v>
       </c>
       <c r="E91" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F91" t="n">
         <v>515663</v>
@@ -7899,7 +7899,7 @@
         <v>-0.002756237978110946</v>
       </c>
       <c r="J91" t="n">
-        <v>69093</v>
+        <v>69095</v>
       </c>
       <c r="K91" t="n">
         <v>356</v>
@@ -7924,7 +7924,7 @@
         <v>28993</v>
       </c>
       <c r="J92" s="6" t="n">
-        <v>69093</v>
+        <v>69095</v>
       </c>
     </row>
   </sheetData>
@@ -11322,7 +11322,7 @@
         <v>-1.223439596904886e-05</v>
       </c>
       <c r="E91" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F91" t="n">
         <v>750284</v>
@@ -11337,7 +11337,7 @@
         <v>-0.002266073672572955</v>
       </c>
       <c r="J91" t="n">
-        <v>79013</v>
+        <v>79057</v>
       </c>
       <c r="K91" t="n">
         <v>677</v>
@@ -11362,7 +11362,7 @@
         <v>94817</v>
       </c>
       <c r="J92" s="6" t="n">
-        <v>79013</v>
+        <v>79057</v>
       </c>
     </row>
   </sheetData>
@@ -14773,7 +14773,7 @@
         <v>0.007075678532743308</v>
       </c>
       <c r="E91" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F91" t="n">
         <v>1158707</v>
@@ -14788,7 +14788,7 @@
         <v>0.003926043490664023</v>
       </c>
       <c r="J91" t="n">
-        <v>140236</v>
+        <v>140233</v>
       </c>
       <c r="K91" t="n">
         <v>0</v>
@@ -14813,7 +14813,7 @@
         <v>115237</v>
       </c>
       <c r="J92" s="6" t="n">
-        <v>140236</v>
+        <v>140233</v>
       </c>
     </row>
   </sheetData>
@@ -18211,22 +18211,22 @@
         <v>0.003988440884456001</v>
       </c>
       <c r="E91" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F91" t="n">
-        <v>527808</v>
+        <v>529511</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
       </c>
       <c r="H91" t="n">
-        <v>167506</v>
+        <v>180393</v>
       </c>
       <c r="I91" s="5" t="n">
-        <v>0.06587178830768477</v>
+        <v>0.08823732300338932</v>
       </c>
       <c r="J91" t="n">
-        <v>79203</v>
+        <v>79201</v>
       </c>
       <c r="K91" t="n">
         <v>262</v>
@@ -18242,16 +18242,16 @@
         <v>83501</v>
       </c>
       <c r="F92" s="6" t="n">
-        <v>292951</v>
+        <v>294654</v>
       </c>
       <c r="G92" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H92" s="6" t="n">
-        <v>167506</v>
+        <v>180393</v>
       </c>
       <c r="J92" s="6" t="n">
-        <v>79203</v>
+        <v>79201</v>
       </c>
     </row>
   </sheetData>
@@ -21649,7 +21649,7 @@
         <v>0.00111791985428869</v>
       </c>
       <c r="E91" t="n">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="F91" t="n">
         <v>1840404</v>
@@ -25102,7 +25102,7 @@
         <v>0.002717387258208371</v>
       </c>
       <c r="J91" t="n">
-        <v>61115</v>
+        <v>61118</v>
       </c>
       <c r="K91" t="n">
         <v>0</v>
@@ -25127,7 +25127,7 @@
         <v>78113</v>
       </c>
       <c r="J92" s="6" t="n">
-        <v>61115</v>
+        <v>61118</v>
       </c>
     </row>
   </sheetData>
@@ -31978,10 +31978,10 @@
         <v>-0.0005151242197594744</v>
       </c>
       <c r="J91" t="n">
-        <v>54706</v>
+        <v>54702</v>
       </c>
       <c r="K91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
@@ -32003,7 +32003,7 @@
         <v>50918</v>
       </c>
       <c r="J92" s="6" t="n">
-        <v>54706</v>
+        <v>54702</v>
       </c>
     </row>
   </sheetData>
@@ -35416,10 +35416,10 @@
         <v>-0.003992581798913764</v>
       </c>
       <c r="J91" t="n">
-        <v>56285</v>
+        <v>56289</v>
       </c>
       <c r="K91" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="92">
@@ -35441,7 +35441,7 @@
         <v>29534</v>
       </c>
       <c r="J92" s="6" t="n">
-        <v>56285</v>
+        <v>56289</v>
       </c>
     </row>
   </sheetData>
@@ -38854,7 +38854,7 @@
         <v>0</v>
       </c>
       <c r="J91" t="n">
-        <v>52712</v>
+        <v>52710</v>
       </c>
       <c r="K91" t="n">
         <v>47</v>
@@ -38879,7 +38879,7 @@
         <v>72</v>
       </c>
       <c r="J92" s="6" t="n">
-        <v>52712</v>
+        <v>52710</v>
       </c>
     </row>
   </sheetData>

--- a/estado/registroRegional.xlsx
+++ b/estado/registroRegional.xlsx
@@ -194,12 +194,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'PNB'!$A$2:$A$91</f>
+              <f>'PNB'!$A$2:$A$92</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'PNB'!$B$2:$B$91</f>
+              <f>'PNB'!$B$2:$B$92</f>
             </numRef>
           </yVal>
         </ser>
@@ -224,12 +224,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'PNB'!$A$2:$A$91</f>
+              <f>'PNB'!$A$2:$A$92</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'PNB'!$F$2:$F$91</f>
+              <f>'PNB'!$F$2:$F$92</f>
             </numRef>
           </yVal>
         </ser>
@@ -255,12 +255,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'PNB'!$A$2:$A$91</f>
+              <f>'PNB'!$A$2:$A$92</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'PNB'!$G$2:$G$91</f>
+              <f>'PNB'!$G$2:$G$92</f>
             </numRef>
           </yVal>
         </ser>
@@ -286,12 +286,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'PNB'!$A$2:$A$91</f>
+              <f>'PNB'!$A$2:$A$92</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'PNB'!$H$2:$H$91</f>
+              <f>'PNB'!$H$2:$H$92</f>
             </numRef>
           </yVal>
         </ser>
@@ -371,12 +371,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'JIM'!$A$2:$A$91</f>
+              <f>'JIM'!$A$2:$A$92</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'JIM'!$J$2:$J$91</f>
+              <f>'JIM'!$J$2:$J$92</f>
             </numRef>
           </yVal>
         </ser>
@@ -401,12 +401,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'JIM'!$A$2:$A$91</f>
+              <f>'JIM'!$A$2:$A$92</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'JIM'!$K$2:$K$91</f>
+              <f>'JIM'!$K$2:$K$92</f>
             </numRef>
           </yVal>
         </ser>
@@ -486,12 +486,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'NDI'!$A$2:$A$91</f>
+              <f>'NDI'!$A$2:$A$92</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'NDI'!$B$2:$B$91</f>
+              <f>'NDI'!$B$2:$B$92</f>
             </numRef>
           </yVal>
         </ser>
@@ -516,12 +516,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'NDI'!$A$2:$A$91</f>
+              <f>'NDI'!$A$2:$A$92</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'NDI'!$F$2:$F$91</f>
+              <f>'NDI'!$F$2:$F$92</f>
             </numRef>
           </yVal>
         </ser>
@@ -547,12 +547,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'NDI'!$A$2:$A$91</f>
+              <f>'NDI'!$A$2:$A$92</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'NDI'!$G$2:$G$91</f>
+              <f>'NDI'!$G$2:$G$92</f>
             </numRef>
           </yVal>
         </ser>
@@ -578,12 +578,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'NDI'!$A$2:$A$91</f>
+              <f>'NDI'!$A$2:$A$92</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'NDI'!$H$2:$H$91</f>
+              <f>'NDI'!$H$2:$H$92</f>
             </numRef>
           </yVal>
         </ser>
@@ -663,12 +663,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'NDI'!$A$2:$A$91</f>
+              <f>'NDI'!$A$2:$A$92</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'NDI'!$J$2:$J$91</f>
+              <f>'NDI'!$J$2:$J$92</f>
             </numRef>
           </yVal>
         </ser>
@@ -693,12 +693,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'NDI'!$A$2:$A$91</f>
+              <f>'NDI'!$A$2:$A$92</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'NDI'!$K$2:$K$91</f>
+              <f>'NDI'!$K$2:$K$92</f>
             </numRef>
           </yVal>
         </ser>
@@ -778,12 +778,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'CXM'!$A$2:$A$91</f>
+              <f>'CXM'!$A$2:$A$92</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'CXM'!$B$2:$B$91</f>
+              <f>'CXM'!$B$2:$B$92</f>
             </numRef>
           </yVal>
         </ser>
@@ -808,12 +808,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'CXM'!$A$2:$A$91</f>
+              <f>'CXM'!$A$2:$A$92</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'CXM'!$F$2:$F$91</f>
+              <f>'CXM'!$F$2:$F$92</f>
             </numRef>
           </yVal>
         </ser>
@@ -839,12 +839,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'CXM'!$A$2:$A$91</f>
+              <f>'CXM'!$A$2:$A$92</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'CXM'!$G$2:$G$91</f>
+              <f>'CXM'!$G$2:$G$92</f>
             </numRef>
           </yVal>
         </ser>
@@ -870,12 +870,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'CXM'!$A$2:$A$91</f>
+              <f>'CXM'!$A$2:$A$92</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'CXM'!$H$2:$H$91</f>
+              <f>'CXM'!$H$2:$H$92</f>
             </numRef>
           </yVal>
         </ser>
@@ -955,12 +955,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'CXM'!$A$2:$A$91</f>
+              <f>'CXM'!$A$2:$A$92</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'CXM'!$J$2:$J$91</f>
+              <f>'CXM'!$J$2:$J$92</f>
             </numRef>
           </yVal>
         </ser>
@@ -985,12 +985,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'CXM'!$A$2:$A$91</f>
+              <f>'CXM'!$A$2:$A$92</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'CXM'!$K$2:$K$91</f>
+              <f>'CXM'!$K$2:$K$92</f>
             </numRef>
           </yVal>
         </ser>
@@ -1070,12 +1070,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'AUA'!$A$2:$A$91</f>
+              <f>'AUA'!$A$2:$A$92</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'AUA'!$B$2:$B$91</f>
+              <f>'AUA'!$B$2:$B$92</f>
             </numRef>
           </yVal>
         </ser>
@@ -1100,12 +1100,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'AUA'!$A$2:$A$91</f>
+              <f>'AUA'!$A$2:$A$92</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'AUA'!$F$2:$F$91</f>
+              <f>'AUA'!$F$2:$F$92</f>
             </numRef>
           </yVal>
         </ser>
@@ -1131,12 +1131,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'AUA'!$A$2:$A$91</f>
+              <f>'AUA'!$A$2:$A$92</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'AUA'!$G$2:$G$91</f>
+              <f>'AUA'!$G$2:$G$92</f>
             </numRef>
           </yVal>
         </ser>
@@ -1162,12 +1162,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'AUA'!$A$2:$A$91</f>
+              <f>'AUA'!$A$2:$A$92</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'AUA'!$H$2:$H$91</f>
+              <f>'AUA'!$H$2:$H$92</f>
             </numRef>
           </yVal>
         </ser>
@@ -1247,12 +1247,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'AUA'!$A$2:$A$91</f>
+              <f>'AUA'!$A$2:$A$92</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'AUA'!$J$2:$J$91</f>
+              <f>'AUA'!$J$2:$J$92</f>
             </numRef>
           </yVal>
         </ser>
@@ -1277,12 +1277,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'AUA'!$A$2:$A$91</f>
+              <f>'AUA'!$A$2:$A$92</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'AUA'!$K$2:$K$91</f>
+              <f>'AUA'!$K$2:$K$92</f>
             </numRef>
           </yVal>
         </ser>
@@ -1362,12 +1362,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'CMA'!$A$2:$A$91</f>
+              <f>'CMA'!$A$2:$A$92</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'CMA'!$B$2:$B$91</f>
+              <f>'CMA'!$B$2:$B$92</f>
             </numRef>
           </yVal>
         </ser>
@@ -1392,12 +1392,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'CMA'!$A$2:$A$91</f>
+              <f>'CMA'!$A$2:$A$92</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'CMA'!$F$2:$F$91</f>
+              <f>'CMA'!$F$2:$F$92</f>
             </numRef>
           </yVal>
         </ser>
@@ -1423,12 +1423,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'CMA'!$A$2:$A$91</f>
+              <f>'CMA'!$A$2:$A$92</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'CMA'!$G$2:$G$91</f>
+              <f>'CMA'!$G$2:$G$92</f>
             </numRef>
           </yVal>
         </ser>
@@ -1454,12 +1454,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'CMA'!$A$2:$A$91</f>
+              <f>'CMA'!$A$2:$A$92</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'CMA'!$H$2:$H$91</f>
+              <f>'CMA'!$H$2:$H$92</f>
             </numRef>
           </yVal>
         </ser>
@@ -1539,12 +1539,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'CMA'!$A$2:$A$91</f>
+              <f>'CMA'!$A$2:$A$92</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'CMA'!$J$2:$J$91</f>
+              <f>'CMA'!$J$2:$J$92</f>
             </numRef>
           </yVal>
         </ser>
@@ -1569,12 +1569,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'CMA'!$A$2:$A$91</f>
+              <f>'CMA'!$A$2:$A$92</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'CMA'!$K$2:$K$91</f>
+              <f>'CMA'!$K$2:$K$92</f>
             </numRef>
           </yVal>
         </ser>
@@ -1654,12 +1654,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'PPR'!$A$2:$A$91</f>
+              <f>'PPR'!$A$2:$A$92</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'PPR'!$B$2:$B$91</f>
+              <f>'PPR'!$B$2:$B$92</f>
             </numRef>
           </yVal>
         </ser>
@@ -1684,12 +1684,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'PPR'!$A$2:$A$91</f>
+              <f>'PPR'!$A$2:$A$92</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'PPR'!$F$2:$F$91</f>
+              <f>'PPR'!$F$2:$F$92</f>
             </numRef>
           </yVal>
         </ser>
@@ -1715,12 +1715,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'PPR'!$A$2:$A$91</f>
+              <f>'PPR'!$A$2:$A$92</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'PPR'!$G$2:$G$91</f>
+              <f>'PPR'!$G$2:$G$92</f>
             </numRef>
           </yVal>
         </ser>
@@ -1746,12 +1746,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'PPR'!$A$2:$A$91</f>
+              <f>'PPR'!$A$2:$A$92</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'PPR'!$H$2:$H$91</f>
+              <f>'PPR'!$H$2:$H$92</f>
             </numRef>
           </yVal>
         </ser>
@@ -1831,12 +1831,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'PNB'!$A$2:$A$91</f>
+              <f>'PNB'!$A$2:$A$92</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'PNB'!$J$2:$J$91</f>
+              <f>'PNB'!$J$2:$J$92</f>
             </numRef>
           </yVal>
         </ser>
@@ -1861,12 +1861,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'PNB'!$A$2:$A$91</f>
+              <f>'PNB'!$A$2:$A$92</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'PNB'!$K$2:$K$91</f>
+              <f>'PNB'!$K$2:$K$92</f>
             </numRef>
           </yVal>
         </ser>
@@ -1946,12 +1946,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'PPR'!$A$2:$A$91</f>
+              <f>'PPR'!$A$2:$A$92</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'PPR'!$J$2:$J$91</f>
+              <f>'PPR'!$J$2:$J$92</f>
             </numRef>
           </yVal>
         </ser>
@@ -1976,12 +1976,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'PPR'!$A$2:$A$91</f>
+              <f>'PPR'!$A$2:$A$92</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'PPR'!$K$2:$K$91</f>
+              <f>'PPR'!$K$2:$K$92</f>
             </numRef>
           </yVal>
         </ser>
@@ -2061,12 +2061,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'TLS'!$A$2:$A$91</f>
+              <f>'TLS'!$A$2:$A$92</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'TLS'!$B$2:$B$91</f>
+              <f>'TLS'!$B$2:$B$92</f>
             </numRef>
           </yVal>
         </ser>
@@ -2091,12 +2091,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'TLS'!$A$2:$A$91</f>
+              <f>'TLS'!$A$2:$A$92</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'TLS'!$F$2:$F$91</f>
+              <f>'TLS'!$F$2:$F$92</f>
             </numRef>
           </yVal>
         </ser>
@@ -2122,12 +2122,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'TLS'!$A$2:$A$91</f>
+              <f>'TLS'!$A$2:$A$92</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'TLS'!$G$2:$G$91</f>
+              <f>'TLS'!$G$2:$G$92</f>
             </numRef>
           </yVal>
         </ser>
@@ -2153,12 +2153,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'TLS'!$A$2:$A$91</f>
+              <f>'TLS'!$A$2:$A$92</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'TLS'!$H$2:$H$91</f>
+              <f>'TLS'!$H$2:$H$92</f>
             </numRef>
           </yVal>
         </ser>
@@ -2238,12 +2238,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'TLS'!$A$2:$A$91</f>
+              <f>'TLS'!$A$2:$A$92</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'TLS'!$J$2:$J$91</f>
+              <f>'TLS'!$J$2:$J$92</f>
             </numRef>
           </yVal>
         </ser>
@@ -2268,12 +2268,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'TLS'!$A$2:$A$91</f>
+              <f>'TLS'!$A$2:$A$92</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'TLS'!$K$2:$K$91</f>
+              <f>'TLS'!$K$2:$K$92</f>
             </numRef>
           </yVal>
         </ser>
@@ -2353,12 +2353,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'NVR'!$A$2:$A$91</f>
+              <f>'NVR'!$A$2:$A$92</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'NVR'!$B$2:$B$91</f>
+              <f>'NVR'!$B$2:$B$92</f>
             </numRef>
           </yVal>
         </ser>
@@ -2383,12 +2383,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'NVR'!$A$2:$A$91</f>
+              <f>'NVR'!$A$2:$A$92</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'NVR'!$F$2:$F$91</f>
+              <f>'NVR'!$F$2:$F$92</f>
             </numRef>
           </yVal>
         </ser>
@@ -2414,12 +2414,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'NVR'!$A$2:$A$91</f>
+              <f>'NVR'!$A$2:$A$92</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'NVR'!$G$2:$G$91</f>
+              <f>'NVR'!$G$2:$G$92</f>
             </numRef>
           </yVal>
         </ser>
@@ -2445,12 +2445,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'NVR'!$A$2:$A$91</f>
+              <f>'NVR'!$A$2:$A$92</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'NVR'!$H$2:$H$91</f>
+              <f>'NVR'!$H$2:$H$92</f>
             </numRef>
           </yVal>
         </ser>
@@ -2530,12 +2530,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'NVR'!$A$2:$A$91</f>
+              <f>'NVR'!$A$2:$A$92</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'NVR'!$J$2:$J$91</f>
+              <f>'NVR'!$J$2:$J$92</f>
             </numRef>
           </yVal>
         </ser>
@@ -2560,12 +2560,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'NVR'!$A$2:$A$91</f>
+              <f>'NVR'!$A$2:$A$92</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'NVR'!$K$2:$K$91</f>
+              <f>'NVR'!$K$2:$K$92</f>
             </numRef>
           </yVal>
         </ser>
@@ -2645,12 +2645,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'DOS'!$A$2:$A$91</f>
+              <f>'DOS'!$A$2:$A$92</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'DOS'!$B$2:$B$91</f>
+              <f>'DOS'!$B$2:$B$92</f>
             </numRef>
           </yVal>
         </ser>
@@ -2675,12 +2675,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'DOS'!$A$2:$A$91</f>
+              <f>'DOS'!$A$2:$A$92</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'DOS'!$F$2:$F$91</f>
+              <f>'DOS'!$F$2:$F$92</f>
             </numRef>
           </yVal>
         </ser>
@@ -2706,12 +2706,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'DOS'!$A$2:$A$91</f>
+              <f>'DOS'!$A$2:$A$92</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'DOS'!$G$2:$G$91</f>
+              <f>'DOS'!$G$2:$G$92</f>
             </numRef>
           </yVal>
         </ser>
@@ -2737,12 +2737,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'DOS'!$A$2:$A$91</f>
+              <f>'DOS'!$A$2:$A$92</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'DOS'!$H$2:$H$91</f>
+              <f>'DOS'!$H$2:$H$92</f>
             </numRef>
           </yVal>
         </ser>
@@ -2822,12 +2822,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'DOS'!$A$2:$A$91</f>
+              <f>'DOS'!$A$2:$A$92</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'DOS'!$J$2:$J$91</f>
+              <f>'DOS'!$J$2:$J$92</f>
             </numRef>
           </yVal>
         </ser>
@@ -2852,12 +2852,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'DOS'!$A$2:$A$91</f>
+              <f>'DOS'!$A$2:$A$92</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'DOS'!$K$2:$K$91</f>
+              <f>'DOS'!$K$2:$K$92</f>
             </numRef>
           </yVal>
         </ser>
@@ -2937,12 +2937,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'JIM'!$A$2:$A$91</f>
+              <f>'JIM'!$A$2:$A$92</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'JIM'!$B$2:$B$91</f>
+              <f>'JIM'!$B$2:$B$92</f>
             </numRef>
           </yVal>
         </ser>
@@ -2967,12 +2967,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'JIM'!$A$2:$A$91</f>
+              <f>'JIM'!$A$2:$A$92</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'JIM'!$F$2:$F$91</f>
+              <f>'JIM'!$F$2:$F$92</f>
             </numRef>
           </yVal>
         </ser>
@@ -2998,12 +2998,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'JIM'!$A$2:$A$91</f>
+              <f>'JIM'!$A$2:$A$92</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'JIM'!$G$2:$G$91</f>
+              <f>'JIM'!$G$2:$G$92</f>
             </numRef>
           </yVal>
         </ser>
@@ -3029,12 +3029,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'JIM'!$A$2:$A$91</f>
+              <f>'JIM'!$A$2:$A$92</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'JIM'!$H$2:$H$91</f>
+              <f>'JIM'!$H$2:$H$92</f>
             </numRef>
           </yVal>
         </ser>
@@ -4502,7 +4502,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K92"/>
+  <dimension ref="A1:K93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -7906,24 +7906,61 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="6" t="inlineStr">
+      <c r="A92" s="4" t="inlineStr">
+        <is>
+          <t>08/2026</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>755277</v>
+      </c>
+      <c r="C92" t="n">
+        <v>0</v>
+      </c>
+      <c r="D92" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E92" t="n">
+        <v>0</v>
+      </c>
+      <c r="F92" t="n">
+        <v>515663</v>
+      </c>
+      <c r="G92" t="n">
+        <v>50527</v>
+      </c>
+      <c r="H92" t="n">
+        <v>28993</v>
+      </c>
+      <c r="I92" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J92" t="n">
+        <v>69095</v>
+      </c>
+      <c r="K92" t="n">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B92" s="6" t="n">
+      <c r="B93" s="6" t="n">
         <v>133520</v>
       </c>
-      <c r="F92" s="6" t="n">
+      <c r="F93" s="6" t="n">
         <v>295002</v>
       </c>
-      <c r="G92" s="6" t="n">
+      <c r="G93" s="6" t="n">
         <v>50527</v>
       </c>
-      <c r="H92" s="6" t="n">
+      <c r="H93" s="6" t="n">
         <v>28993</v>
       </c>
-      <c r="J92" s="6" t="n">
+      <c r="J93" s="6" t="n">
         <v>69095</v>
       </c>
     </row>
@@ -7940,7 +7977,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K92"/>
+  <dimension ref="A1:K93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -11322,7 +11359,7 @@
         <v>-1.223439596904886e-05</v>
       </c>
       <c r="E91" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F91" t="n">
         <v>750284</v>
@@ -11344,25 +11381,62 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="6" t="inlineStr">
+      <c r="A92" s="4" t="inlineStr">
+        <is>
+          <t>08/2026</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>1062565</v>
+      </c>
+      <c r="C92" t="n">
+        <v>0</v>
+      </c>
+      <c r="D92" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E92" t="n">
+        <v>0</v>
+      </c>
+      <c r="F92" t="n">
+        <v>750284</v>
+      </c>
+      <c r="G92" t="n">
+        <v>26677</v>
+      </c>
+      <c r="H92" t="n">
+        <v>94817</v>
+      </c>
+      <c r="I92" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J92" t="n">
+        <v>79222</v>
+      </c>
+      <c r="K92" t="n">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B92" s="6" t="n">
+      <c r="B93" s="6" t="n">
         <v>213139</v>
       </c>
-      <c r="F92" s="6" t="n">
+      <c r="F93" s="6" t="n">
         <v>251377</v>
       </c>
-      <c r="G92" s="6" t="n">
+      <c r="G93" s="6" t="n">
         <v>26677</v>
       </c>
-      <c r="H92" s="6" t="n">
+      <c r="H93" s="6" t="n">
         <v>94817</v>
       </c>
-      <c r="J92" s="6" t="n">
-        <v>79057</v>
+      <c r="J93" s="6" t="n">
+        <v>79222</v>
       </c>
     </row>
   </sheetData>
@@ -11391,7 +11465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K92"/>
+  <dimension ref="A1:K93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -14773,7 +14847,7 @@
         <v>0.007075678532743308</v>
       </c>
       <c r="E91" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="F91" t="n">
         <v>1158707</v>
@@ -14795,25 +14869,62 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="6" t="inlineStr">
+      <c r="A92" s="4" t="inlineStr">
+        <is>
+          <t>08/2026</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>1702114</v>
+      </c>
+      <c r="C92" t="n">
+        <v>0</v>
+      </c>
+      <c r="D92" s="5" t="n">
+        <v>0.001506866805565934</v>
+      </c>
+      <c r="E92" t="n">
+        <v>1</v>
+      </c>
+      <c r="F92" t="n">
+        <v>1158707</v>
+      </c>
+      <c r="G92" t="n">
+        <v>0</v>
+      </c>
+      <c r="H92" t="n">
+        <v>115237</v>
+      </c>
+      <c r="I92" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J92" t="n">
+        <v>140239</v>
+      </c>
+      <c r="K92" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B92" s="6" t="n">
-        <v>492202</v>
-      </c>
-      <c r="F92" s="6" t="n">
+      <c r="B93" s="6" t="n">
+        <v>494763</v>
+      </c>
+      <c r="F93" s="6" t="n">
         <v>616111</v>
       </c>
-      <c r="G92" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H92" s="6" t="n">
+      <c r="G93" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H93" s="6" t="n">
         <v>115237</v>
       </c>
-      <c r="J92" s="6" t="n">
-        <v>140233</v>
+      <c r="J93" s="6" t="n">
+        <v>140239</v>
       </c>
     </row>
   </sheetData>
@@ -14829,7 +14940,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K92"/>
+  <dimension ref="A1:K93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -18233,24 +18344,61 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="6" t="inlineStr">
+      <c r="A92" s="4" t="inlineStr">
+        <is>
+          <t>08/2026</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>1213564</v>
+      </c>
+      <c r="C92" t="n">
+        <v>0</v>
+      </c>
+      <c r="D92" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E92" t="n">
+        <v>0</v>
+      </c>
+      <c r="F92" t="n">
+        <v>529511</v>
+      </c>
+      <c r="G92" t="n">
+        <v>0</v>
+      </c>
+      <c r="H92" t="n">
+        <v>180393</v>
+      </c>
+      <c r="I92" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J92" t="n">
+        <v>79201</v>
+      </c>
+      <c r="K92" t="n">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B92" s="6" t="n">
+      <c r="B93" s="6" t="n">
         <v>83501</v>
       </c>
-      <c r="F92" s="6" t="n">
+      <c r="F93" s="6" t="n">
         <v>294654</v>
       </c>
-      <c r="G92" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H92" s="6" t="n">
+      <c r="G93" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H93" s="6" t="n">
         <v>180393</v>
       </c>
-      <c r="J92" s="6" t="n">
+      <c r="J93" s="6" t="n">
         <v>79201</v>
       </c>
     </row>
@@ -18267,7 +18415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K92"/>
+  <dimension ref="A1:K93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -21649,7 +21797,7 @@
         <v>0.00111791985428869</v>
       </c>
       <c r="E91" t="n">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="F91" t="n">
         <v>1840404</v>
@@ -21671,24 +21819,61 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="6" t="inlineStr">
+      <c r="A92" s="4" t="inlineStr">
+        <is>
+          <t>08/2026</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>3071750</v>
+      </c>
+      <c r="C92" t="n">
+        <v>49144</v>
+      </c>
+      <c r="D92" s="5" t="n">
+        <v>3.845066875325629e-06</v>
+      </c>
+      <c r="E92" t="n">
+        <v>5</v>
+      </c>
+      <c r="F92" t="n">
+        <v>1840404</v>
+      </c>
+      <c r="G92" t="n">
+        <v>123505</v>
+      </c>
+      <c r="H92" t="n">
+        <v>134758</v>
+      </c>
+      <c r="I92" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J92" t="n">
+        <v>188889</v>
+      </c>
+      <c r="K92" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B92" s="6" t="n">
-        <v>735917</v>
-      </c>
-      <c r="F92" s="6" t="n">
+      <c r="B93" s="6" t="n">
+        <v>735929</v>
+      </c>
+      <c r="F93" s="6" t="n">
         <v>955940</v>
       </c>
-      <c r="G92" s="6" t="n">
+      <c r="G93" s="6" t="n">
         <v>123505</v>
       </c>
-      <c r="H92" s="6" t="n">
+      <c r="H93" s="6" t="n">
         <v>134758</v>
       </c>
-      <c r="J92" s="6" t="n">
+      <c r="J93" s="6" t="n">
         <v>188889</v>
       </c>
     </row>
@@ -21705,7 +21890,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K92"/>
+  <dimension ref="A1:K93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -25087,7 +25272,7 @@
         <v>0.0008746660582033218</v>
       </c>
       <c r="E91" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F91" t="n">
         <v>590365</v>
@@ -25109,24 +25294,61 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="6" t="inlineStr">
+      <c r="A92" s="4" t="inlineStr">
+        <is>
+          <t>08/2026</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>947475</v>
+      </c>
+      <c r="C92" t="n">
+        <v>0</v>
+      </c>
+      <c r="D92" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E92" t="n">
+        <v>0</v>
+      </c>
+      <c r="F92" t="n">
+        <v>590365</v>
+      </c>
+      <c r="G92" t="n">
+        <v>4948</v>
+      </c>
+      <c r="H92" t="n">
+        <v>78113</v>
+      </c>
+      <c r="I92" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J92" t="n">
+        <v>61118</v>
+      </c>
+      <c r="K92" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B92" s="6" t="n">
+      <c r="B93" s="6" t="n">
         <v>218585</v>
       </c>
-      <c r="F92" s="6" t="n">
+      <c r="F93" s="6" t="n">
         <v>358194</v>
       </c>
-      <c r="G92" s="6" t="n">
+      <c r="G93" s="6" t="n">
         <v>4948</v>
       </c>
-      <c r="H92" s="6" t="n">
+      <c r="H93" s="6" t="n">
         <v>78113</v>
       </c>
-      <c r="J92" s="6" t="n">
+      <c r="J93" s="6" t="n">
         <v>61118</v>
       </c>
     </row>
@@ -25143,7 +25365,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K92"/>
+  <dimension ref="A1:K93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -28547,24 +28769,61 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="6" t="inlineStr">
+      <c r="A92" s="4" t="inlineStr">
+        <is>
+          <t>08/2026</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>935351</v>
+      </c>
+      <c r="C92" t="n">
+        <v>11614</v>
+      </c>
+      <c r="D92" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E92" t="n">
+        <v>0</v>
+      </c>
+      <c r="F92" t="n">
+        <v>500352</v>
+      </c>
+      <c r="G92" t="n">
+        <v>6655</v>
+      </c>
+      <c r="H92" t="n">
+        <v>101039</v>
+      </c>
+      <c r="I92" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J92" t="n">
+        <v>66009</v>
+      </c>
+      <c r="K92" t="n">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B92" s="6" t="n">
+      <c r="B93" s="6" t="n">
         <v>92870</v>
       </c>
-      <c r="F92" s="6" t="n">
+      <c r="F93" s="6" t="n">
         <v>225440</v>
       </c>
-      <c r="G92" s="6" t="n">
+      <c r="G93" s="6" t="n">
         <v>6655</v>
       </c>
-      <c r="H92" s="6" t="n">
+      <c r="H93" s="6" t="n">
         <v>101039</v>
       </c>
-      <c r="J92" s="6" t="n">
+      <c r="J93" s="6" t="n">
         <v>66009</v>
       </c>
     </row>
@@ -28581,7 +28840,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K92"/>
+  <dimension ref="A1:K93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -31985,24 +32244,61 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="6" t="inlineStr">
+      <c r="A92" s="4" t="inlineStr">
+        <is>
+          <t>08/2026</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>801312</v>
+      </c>
+      <c r="C92" t="n">
+        <v>0</v>
+      </c>
+      <c r="D92" s="5" t="n">
+        <v>-0.000250775720418758</v>
+      </c>
+      <c r="E92" t="n">
+        <v>0</v>
+      </c>
+      <c r="F92" t="n">
+        <v>296309</v>
+      </c>
+      <c r="G92" t="n">
+        <v>83</v>
+      </c>
+      <c r="H92" t="n">
+        <v>50918</v>
+      </c>
+      <c r="I92" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J92" t="n">
+        <v>54702</v>
+      </c>
+      <c r="K92" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B92" s="6" t="n">
-        <v>107677</v>
-      </c>
-      <c r="F92" s="6" t="n">
+      <c r="B93" s="6" t="n">
+        <v>107476</v>
+      </c>
+      <c r="F93" s="6" t="n">
         <v>189902</v>
       </c>
-      <c r="G92" s="6" t="n">
+      <c r="G93" s="6" t="n">
         <v>83</v>
       </c>
-      <c r="H92" s="6" t="n">
+      <c r="H93" s="6" t="n">
         <v>50918</v>
       </c>
-      <c r="J92" s="6" t="n">
+      <c r="J93" s="6" t="n">
         <v>54702</v>
       </c>
     </row>
@@ -32019,7 +32315,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K92"/>
+  <dimension ref="A1:K93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -35401,7 +35697,7 @@
         <v>0.0002546138713637119</v>
       </c>
       <c r="E91" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F91" t="n">
         <v>346409</v>
@@ -35423,24 +35719,61 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="6" t="inlineStr">
+      <c r="A92" s="4" t="inlineStr">
+        <is>
+          <t>08/2026</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>746418</v>
+      </c>
+      <c r="C92" t="n">
+        <v>0</v>
+      </c>
+      <c r="D92" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E92" t="n">
+        <v>0</v>
+      </c>
+      <c r="F92" t="n">
+        <v>346409</v>
+      </c>
+      <c r="G92" t="n">
+        <v>0</v>
+      </c>
+      <c r="H92" t="n">
+        <v>29534</v>
+      </c>
+      <c r="I92" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J92" t="n">
+        <v>56289</v>
+      </c>
+      <c r="K92" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B92" s="6" t="n">
+      <c r="B93" s="6" t="n">
         <v>255487</v>
       </c>
-      <c r="F92" s="6" t="n">
+      <c r="F93" s="6" t="n">
         <v>264988</v>
       </c>
-      <c r="G92" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H92" s="6" t="n">
+      <c r="G93" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H93" s="6" t="n">
         <v>29534</v>
       </c>
-      <c r="J92" s="6" t="n">
+      <c r="J93" s="6" t="n">
         <v>56289</v>
       </c>
     </row>
@@ -35457,7 +35790,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K92"/>
+  <dimension ref="A1:K93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -38861,25 +39194,62 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="6" t="inlineStr">
+      <c r="A92" s="4" t="inlineStr">
+        <is>
+          <t>08/2026</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>510824</v>
+      </c>
+      <c r="C92" t="n">
+        <v>0</v>
+      </c>
+      <c r="D92" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E92" t="n">
+        <v>0</v>
+      </c>
+      <c r="F92" t="n">
+        <v>295759</v>
+      </c>
+      <c r="G92" t="n">
+        <v>0</v>
+      </c>
+      <c r="H92" t="n">
+        <v>72</v>
+      </c>
+      <c r="I92" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J92" t="n">
+        <v>52716</v>
+      </c>
+      <c r="K92" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B92" s="6" t="n">
+      <c r="B93" s="6" t="n">
         <v>-99901</v>
       </c>
-      <c r="F92" s="6" t="n">
+      <c r="F93" s="6" t="n">
         <v>-7808</v>
       </c>
-      <c r="G92" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H92" s="6" t="n">
+      <c r="G93" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H93" s="6" t="n">
         <v>72</v>
       </c>
-      <c r="J92" s="6" t="n">
-        <v>52710</v>
+      <c r="J93" s="6" t="n">
+        <v>52716</v>
       </c>
     </row>
   </sheetData>

--- a/estado/registroRegional.xlsx
+++ b/estado/registroRegional.xlsx
@@ -7921,7 +7921,7 @@
         <v>0</v>
       </c>
       <c r="E92" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F92" t="n">
         <v>515663</v>
@@ -11396,7 +11396,7 @@
         <v>0</v>
       </c>
       <c r="E92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F92" t="n">
         <v>750284</v>
@@ -14884,7 +14884,7 @@
         <v>0.001506866805565934</v>
       </c>
       <c r="E92" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F92" t="n">
         <v>1158707</v>
@@ -21825,16 +21825,16 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>3071750</v>
+        <v>3072162</v>
       </c>
       <c r="C92" t="n">
         <v>49144</v>
       </c>
       <c r="D92" s="5" t="n">
-        <v>3.845066875325629e-06</v>
+        <v>0.0001358590295948389</v>
       </c>
       <c r="E92" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F92" t="n">
         <v>1840404</v>
@@ -21862,7 +21862,7 @@
         </is>
       </c>
       <c r="B93" s="6" t="n">
-        <v>735929</v>
+        <v>736341</v>
       </c>
       <c r="F93" s="6" t="n">
         <v>955940</v>
@@ -25309,7 +25309,7 @@
         <v>0</v>
       </c>
       <c r="E92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F92" t="n">
         <v>590365</v>
@@ -28784,7 +28784,7 @@
         <v>0</v>
       </c>
       <c r="E92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F92" t="n">
         <v>500352</v>
@@ -39209,7 +39209,7 @@
         <v>0</v>
       </c>
       <c r="E92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F92" t="n">
         <v>295759</v>

--- a/estado/registroRegional.xlsx
+++ b/estado/registroRegional.xlsx
@@ -11396,7 +11396,7 @@
         <v>0</v>
       </c>
       <c r="E92" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F92" t="n">
         <v>750284</v>
@@ -14875,16 +14875,16 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>1702114</v>
+        <v>1710985</v>
       </c>
       <c r="C92" t="n">
         <v>0</v>
       </c>
       <c r="D92" s="5" t="n">
-        <v>0.001506866805565934</v>
+        <v>0.006726474549484482</v>
       </c>
       <c r="E92" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F92" t="n">
         <v>1158707</v>
@@ -14912,7 +14912,7 @@
         </is>
       </c>
       <c r="B93" s="6" t="n">
-        <v>494763</v>
+        <v>503634</v>
       </c>
       <c r="F93" s="6" t="n">
         <v>616111</v>
@@ -21834,7 +21834,7 @@
         <v>0.0001358590295948389</v>
       </c>
       <c r="E92" t="n">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="F92" t="n">
         <v>1840404</v>
@@ -25309,7 +25309,7 @@
         <v>0</v>
       </c>
       <c r="E92" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F92" t="n">
         <v>590365</v>
@@ -25324,7 +25324,7 @@
         <v>0</v>
       </c>
       <c r="J92" t="n">
-        <v>61118</v>
+        <v>61117</v>
       </c>
       <c r="K92" t="n">
         <v>0</v>
@@ -25349,7 +25349,7 @@
         <v>78113</v>
       </c>
       <c r="J93" s="6" t="n">
-        <v>61118</v>
+        <v>61117</v>
       </c>
     </row>
   </sheetData>
@@ -28784,7 +28784,7 @@
         <v>0</v>
       </c>
       <c r="E92" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F92" t="n">
         <v>500352</v>
@@ -32259,7 +32259,7 @@
         <v>-0.000250775720418758</v>
       </c>
       <c r="E92" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F92" t="n">
         <v>296309</v>
@@ -35734,7 +35734,7 @@
         <v>0</v>
       </c>
       <c r="E92" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F92" t="n">
         <v>346409</v>
@@ -35752,7 +35752,7 @@
         <v>56289</v>
       </c>
       <c r="K92" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="93">

--- a/estado/registroRegional.xlsx
+++ b/estado/registroRegional.xlsx
@@ -7939,7 +7939,7 @@
         <v>69095</v>
       </c>
       <c r="K92" t="n">
-        <v>354</v>
+        <v>374</v>
       </c>
     </row>
     <row r="93">
@@ -11396,7 +11396,7 @@
         <v>0</v>
       </c>
       <c r="E92" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F92" t="n">
         <v>750284</v>
@@ -11414,7 +11414,7 @@
         <v>79222</v>
       </c>
       <c r="K92" t="n">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="93">
@@ -14899,7 +14899,7 @@
         <v>0</v>
       </c>
       <c r="J92" t="n">
-        <v>140239</v>
+        <v>140247</v>
       </c>
       <c r="K92" t="n">
         <v>0</v>
@@ -14924,7 +14924,7 @@
         <v>115237</v>
       </c>
       <c r="J93" s="6" t="n">
-        <v>140239</v>
+        <v>140247</v>
       </c>
     </row>
   </sheetData>
@@ -18377,7 +18377,7 @@
         <v>79201</v>
       </c>
       <c r="K92" t="n">
-        <v>263</v>
+        <v>277</v>
       </c>
     </row>
     <row r="93">
@@ -21834,7 +21834,7 @@
         <v>0.0001358590295948389</v>
       </c>
       <c r="E92" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="F92" t="n">
         <v>1840404</v>
@@ -21852,7 +21852,7 @@
         <v>188889</v>
       </c>
       <c r="K92" t="n">
-        <v>2</v>
+        <v>29</v>
       </c>
     </row>
     <row r="93">
@@ -25300,13 +25300,13 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>947475</v>
+        <v>947488</v>
       </c>
       <c r="C92" t="n">
         <v>0</v>
       </c>
       <c r="D92" s="5" t="n">
-        <v>0</v>
+        <v>1.372067864587456e-05</v>
       </c>
       <c r="E92" t="n">
         <v>2</v>
@@ -25327,7 +25327,7 @@
         <v>61117</v>
       </c>
       <c r="K92" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="93">
@@ -25337,7 +25337,7 @@
         </is>
       </c>
       <c r="B93" s="6" t="n">
-        <v>218585</v>
+        <v>218598</v>
       </c>
       <c r="F93" s="6" t="n">
         <v>358194</v>
@@ -28802,7 +28802,7 @@
         <v>66009</v>
       </c>
       <c r="K92" t="n">
-        <v>190</v>
+        <v>203</v>
       </c>
     </row>
     <row r="93">
@@ -32274,7 +32274,7 @@
         <v>0</v>
       </c>
       <c r="J92" t="n">
-        <v>54702</v>
+        <v>54712</v>
       </c>
       <c r="K92" t="n">
         <v>0</v>
@@ -32299,7 +32299,7 @@
         <v>50918</v>
       </c>
       <c r="J93" s="6" t="n">
-        <v>54702</v>
+        <v>54712</v>
       </c>
     </row>
   </sheetData>
@@ -35737,22 +35737,22 @@
         <v>4</v>
       </c>
       <c r="F92" t="n">
-        <v>346409</v>
+        <v>324209</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
       </c>
       <c r="H92" t="n">
-        <v>29534</v>
+        <v>29138</v>
       </c>
       <c r="I92" s="5" t="n">
-        <v>0</v>
+        <v>-0.06010485632130403</v>
       </c>
       <c r="J92" t="n">
         <v>56289</v>
       </c>
       <c r="K92" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
     </row>
     <row r="93">
@@ -35765,13 +35765,13 @@
         <v>255487</v>
       </c>
       <c r="F93" s="6" t="n">
-        <v>264988</v>
+        <v>242788</v>
       </c>
       <c r="G93" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H93" s="6" t="n">
-        <v>29534</v>
+        <v>29138</v>
       </c>
       <c r="J93" s="6" t="n">
         <v>56289</v>
@@ -39227,7 +39227,7 @@
         <v>52716</v>
       </c>
       <c r="K92" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="93">

--- a/estado/registroRegional.xlsx
+++ b/estado/registroRegional.xlsx
@@ -7939,7 +7939,7 @@
         <v>69095</v>
       </c>
       <c r="K92" t="n">
-        <v>374</v>
+        <v>396</v>
       </c>
     </row>
     <row r="93">
@@ -11414,7 +11414,7 @@
         <v>79222</v>
       </c>
       <c r="K92" t="n">
-        <v>498</v>
+        <v>502</v>
       </c>
     </row>
     <row r="93">
@@ -14902,7 +14902,7 @@
         <v>140247</v>
       </c>
       <c r="K92" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="93">
@@ -18377,7 +18377,7 @@
         <v>79201</v>
       </c>
       <c r="K92" t="n">
-        <v>277</v>
+        <v>284</v>
       </c>
     </row>
     <row r="93">
@@ -21834,7 +21834,7 @@
         <v>0.0001358590295948389</v>
       </c>
       <c r="E92" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="F92" t="n">
         <v>1840404</v>
@@ -21852,7 +21852,7 @@
         <v>188889</v>
       </c>
       <c r="K92" t="n">
-        <v>29</v>
+        <v>59</v>
       </c>
     </row>
     <row r="93">
@@ -25327,7 +25327,7 @@
         <v>61117</v>
       </c>
       <c r="K92" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
     </row>
     <row r="93">
@@ -28802,7 +28802,7 @@
         <v>66009</v>
       </c>
       <c r="K92" t="n">
-        <v>203</v>
+        <v>212</v>
       </c>
     </row>
     <row r="93">
@@ -32277,7 +32277,7 @@
         <v>54712</v>
       </c>
       <c r="K92" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="93">
@@ -35752,7 +35752,7 @@
         <v>56289</v>
       </c>
       <c r="K92" t="n">
-        <v>37</v>
+        <v>47</v>
       </c>
     </row>
     <row r="93">
@@ -39227,7 +39227,7 @@
         <v>52716</v>
       </c>
       <c r="K92" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="93">

--- a/estado/registroRegional.xlsx
+++ b/estado/registroRegional.xlsx
@@ -7939,7 +7939,7 @@
         <v>69095</v>
       </c>
       <c r="K92" t="n">
-        <v>396</v>
+        <v>411</v>
       </c>
     </row>
     <row r="93">
@@ -11414,7 +11414,7 @@
         <v>79222</v>
       </c>
       <c r="K92" t="n">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="93">
@@ -14902,7 +14902,7 @@
         <v>140247</v>
       </c>
       <c r="K92" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
     </row>
     <row r="93">
@@ -18377,7 +18377,7 @@
         <v>79201</v>
       </c>
       <c r="K92" t="n">
-        <v>284</v>
+        <v>289</v>
       </c>
     </row>
     <row r="93">
@@ -21834,7 +21834,7 @@
         <v>0.0001358590295948389</v>
       </c>
       <c r="E92" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F92" t="n">
         <v>1840404</v>
@@ -21852,7 +21852,7 @@
         <v>188889</v>
       </c>
       <c r="K92" t="n">
-        <v>59</v>
+        <v>114</v>
       </c>
     </row>
     <row r="93">
@@ -25327,7 +25327,7 @@
         <v>61117</v>
       </c>
       <c r="K92" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="93">
@@ -28802,7 +28802,7 @@
         <v>66009</v>
       </c>
       <c r="K92" t="n">
-        <v>212</v>
+        <v>218</v>
       </c>
     </row>
     <row r="93">
@@ -32277,7 +32277,7 @@
         <v>54712</v>
       </c>
       <c r="K92" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="93">
@@ -35752,7 +35752,7 @@
         <v>56289</v>
       </c>
       <c r="K92" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="93">
@@ -39227,7 +39227,7 @@
         <v>52716</v>
       </c>
       <c r="K92" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="93">

--- a/estado/registroRegional.xlsx
+++ b/estado/registroRegional.xlsx
@@ -7921,7 +7921,7 @@
         <v>0</v>
       </c>
       <c r="E92" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F92" t="n">
         <v>515663</v>
@@ -7936,10 +7936,10 @@
         <v>0</v>
       </c>
       <c r="J92" t="n">
-        <v>69095</v>
+        <v>69208</v>
       </c>
       <c r="K92" t="n">
-        <v>411</v>
+        <v>434</v>
       </c>
     </row>
     <row r="93">
@@ -7961,7 +7961,7 @@
         <v>28993</v>
       </c>
       <c r="J93" s="6" t="n">
-        <v>69095</v>
+        <v>69208</v>
       </c>
     </row>
   </sheetData>
@@ -11387,16 +11387,16 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>1062565</v>
+        <v>1076576</v>
       </c>
       <c r="C92" t="n">
         <v>0</v>
       </c>
       <c r="D92" s="5" t="n">
-        <v>0</v>
+        <v>0.01318601685543943</v>
       </c>
       <c r="E92" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="F92" t="n">
         <v>750284</v>
@@ -11414,7 +11414,7 @@
         <v>79222</v>
       </c>
       <c r="K92" t="n">
-        <v>504</v>
+        <v>558</v>
       </c>
     </row>
     <row r="93">
@@ -11424,7 +11424,7 @@
         </is>
       </c>
       <c r="B93" s="6" t="n">
-        <v>213139</v>
+        <v>227150</v>
       </c>
       <c r="F93" s="6" t="n">
         <v>251377</v>
@@ -14875,19 +14875,19 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>1710985</v>
+        <v>1713695</v>
       </c>
       <c r="C92" t="n">
         <v>0</v>
       </c>
       <c r="D92" s="5" t="n">
-        <v>0.006726474549484482</v>
+        <v>0.008321011465956048</v>
       </c>
       <c r="E92" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F92" t="n">
-        <v>1158707</v>
+        <v>1158193</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -14896,13 +14896,13 @@
         <v>115237</v>
       </c>
       <c r="I92" s="5" t="n">
-        <v>0</v>
+        <v>-0.000403471424175631</v>
       </c>
       <c r="J92" t="n">
-        <v>140247</v>
+        <v>140348</v>
       </c>
       <c r="K92" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
     </row>
     <row r="93">
@@ -14912,10 +14912,10 @@
         </is>
       </c>
       <c r="B93" s="6" t="n">
-        <v>503634</v>
+        <v>506344</v>
       </c>
       <c r="F93" s="6" t="n">
-        <v>616111</v>
+        <v>615597</v>
       </c>
       <c r="G93" s="6" t="n">
         <v>0</v>
@@ -14924,7 +14924,7 @@
         <v>115237</v>
       </c>
       <c r="J93" s="6" t="n">
-        <v>140247</v>
+        <v>140348</v>
       </c>
     </row>
   </sheetData>
@@ -18350,34 +18350,34 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>1213564</v>
+        <v>1219217</v>
       </c>
       <c r="C92" t="n">
         <v>0</v>
       </c>
       <c r="D92" s="5" t="n">
-        <v>0</v>
+        <v>0.004658180367908079</v>
       </c>
       <c r="E92" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F92" t="n">
-        <v>529511</v>
+        <v>531351</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
       </c>
       <c r="H92" t="n">
-        <v>180393</v>
+        <v>230671</v>
       </c>
       <c r="I92" s="5" t="n">
-        <v>0</v>
+        <v>0.07341556041380243</v>
       </c>
       <c r="J92" t="n">
         <v>79201</v>
       </c>
       <c r="K92" t="n">
-        <v>289</v>
+        <v>328</v>
       </c>
     </row>
     <row r="93">
@@ -18387,16 +18387,16 @@
         </is>
       </c>
       <c r="B93" s="6" t="n">
-        <v>83501</v>
+        <v>89154</v>
       </c>
       <c r="F93" s="6" t="n">
-        <v>294654</v>
+        <v>296494</v>
       </c>
       <c r="G93" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H93" s="6" t="n">
-        <v>180393</v>
+        <v>230671</v>
       </c>
       <c r="J93" s="6" t="n">
         <v>79201</v>
@@ -21834,22 +21834,22 @@
         <v>0.0001358590295948389</v>
       </c>
       <c r="E92" t="n">
-        <v>54</v>
+        <v>106</v>
       </c>
       <c r="F92" t="n">
-        <v>1840404</v>
+        <v>1842767</v>
       </c>
       <c r="G92" t="n">
         <v>123505</v>
       </c>
       <c r="H92" t="n">
-        <v>134758</v>
+        <v>154953</v>
       </c>
       <c r="I92" s="5" t="n">
-        <v>0</v>
+        <v>0.0107487276447383</v>
       </c>
       <c r="J92" t="n">
-        <v>188889</v>
+        <v>189012</v>
       </c>
       <c r="K92" t="n">
         <v>114</v>
@@ -21865,16 +21865,16 @@
         <v>736341</v>
       </c>
       <c r="F93" s="6" t="n">
-        <v>955940</v>
+        <v>958303</v>
       </c>
       <c r="G93" s="6" t="n">
         <v>123505</v>
       </c>
       <c r="H93" s="6" t="n">
-        <v>134758</v>
+        <v>154953</v>
       </c>
       <c r="J93" s="6" t="n">
-        <v>188889</v>
+        <v>189012</v>
       </c>
     </row>
   </sheetData>
@@ -25300,16 +25300,16 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>947488</v>
+        <v>956245</v>
       </c>
       <c r="C92" t="n">
         <v>0</v>
       </c>
       <c r="D92" s="5" t="n">
-        <v>1.372067864587456e-05</v>
+        <v>0.009256180901870761</v>
       </c>
       <c r="E92" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F92" t="n">
         <v>590365</v>
@@ -25324,10 +25324,10 @@
         <v>0</v>
       </c>
       <c r="J92" t="n">
-        <v>61117</v>
+        <v>61166</v>
       </c>
       <c r="K92" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
     </row>
     <row r="93">
@@ -25337,7 +25337,7 @@
         </is>
       </c>
       <c r="B93" s="6" t="n">
-        <v>218598</v>
+        <v>227355</v>
       </c>
       <c r="F93" s="6" t="n">
         <v>358194</v>
@@ -25349,7 +25349,7 @@
         <v>78113</v>
       </c>
       <c r="J93" s="6" t="n">
-        <v>61117</v>
+        <v>61166</v>
       </c>
     </row>
   </sheetData>
@@ -28784,7 +28784,7 @@
         <v>0</v>
       </c>
       <c r="E92" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F92" t="n">
         <v>500352</v>
@@ -28799,10 +28799,10 @@
         <v>0</v>
       </c>
       <c r="J92" t="n">
-        <v>66009</v>
+        <v>66064</v>
       </c>
       <c r="K92" t="n">
-        <v>218</v>
+        <v>211</v>
       </c>
     </row>
     <row r="93">
@@ -28824,7 +28824,7 @@
         <v>101039</v>
       </c>
       <c r="J93" s="6" t="n">
-        <v>66009</v>
+        <v>66064</v>
       </c>
     </row>
   </sheetData>
@@ -32250,16 +32250,16 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>801312</v>
+        <v>801352</v>
       </c>
       <c r="C92" t="n">
         <v>0</v>
       </c>
       <c r="D92" s="5" t="n">
-        <v>-0.000250775720418758</v>
+        <v>-0.0002008701044150251</v>
       </c>
       <c r="E92" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F92" t="n">
         <v>296309</v>
@@ -32274,10 +32274,10 @@
         <v>0</v>
       </c>
       <c r="J92" t="n">
-        <v>54712</v>
+        <v>54738</v>
       </c>
       <c r="K92" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="93">
@@ -32287,7 +32287,7 @@
         </is>
       </c>
       <c r="B93" s="6" t="n">
-        <v>107476</v>
+        <v>107516</v>
       </c>
       <c r="F93" s="6" t="n">
         <v>189902</v>
@@ -32299,7 +32299,7 @@
         <v>50918</v>
       </c>
       <c r="J93" s="6" t="n">
-        <v>54712</v>
+        <v>54738</v>
       </c>
     </row>
   </sheetData>
@@ -35725,34 +35725,34 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>746418</v>
+        <v>746643</v>
       </c>
       <c r="C92" t="n">
         <v>0</v>
       </c>
       <c r="D92" s="5" t="n">
-        <v>0</v>
+        <v>0.0003014396758920605</v>
       </c>
       <c r="E92" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F92" t="n">
-        <v>324209</v>
+        <v>358823</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
       </c>
       <c r="H92" t="n">
-        <v>29138</v>
+        <v>28881</v>
       </c>
       <c r="I92" s="5" t="n">
-        <v>-0.06010485632130403</v>
+        <v>0.0312839978400981</v>
       </c>
       <c r="J92" t="n">
-        <v>56289</v>
+        <v>56300</v>
       </c>
       <c r="K92" t="n">
-        <v>50</v>
+        <v>93</v>
       </c>
     </row>
     <row r="93">
@@ -35762,19 +35762,19 @@
         </is>
       </c>
       <c r="B93" s="6" t="n">
-        <v>255487</v>
+        <v>255712</v>
       </c>
       <c r="F93" s="6" t="n">
-        <v>242788</v>
+        <v>277402</v>
       </c>
       <c r="G93" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H93" s="6" t="n">
-        <v>29138</v>
+        <v>28881</v>
       </c>
       <c r="J93" s="6" t="n">
-        <v>56289</v>
+        <v>56300</v>
       </c>
     </row>
   </sheetData>
@@ -39224,10 +39224,10 @@
         <v>0</v>
       </c>
       <c r="J92" t="n">
-        <v>52716</v>
+        <v>52757</v>
       </c>
       <c r="K92" t="n">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="93">
@@ -39249,7 +39249,7 @@
         <v>72</v>
       </c>
       <c r="J93" s="6" t="n">
-        <v>52716</v>
+        <v>52757</v>
       </c>
     </row>
   </sheetData>

--- a/estado/registroRegional.xlsx
+++ b/estado/registroRegional.xlsx
@@ -7939,7 +7939,7 @@
         <v>69208</v>
       </c>
       <c r="K92" t="n">
-        <v>434</v>
+        <v>457</v>
       </c>
     </row>
     <row r="93">
@@ -11414,7 +11414,7 @@
         <v>79222</v>
       </c>
       <c r="K92" t="n">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="93">
@@ -14902,7 +14902,7 @@
         <v>140348</v>
       </c>
       <c r="K92" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
     </row>
     <row r="93">
@@ -18377,7 +18377,7 @@
         <v>79201</v>
       </c>
       <c r="K92" t="n">
-        <v>328</v>
+        <v>340</v>
       </c>
     </row>
     <row r="93">
@@ -21834,7 +21834,7 @@
         <v>0.0001358590295948389</v>
       </c>
       <c r="E92" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F92" t="n">
         <v>1842767</v>
@@ -21852,7 +21852,7 @@
         <v>189012</v>
       </c>
       <c r="K92" t="n">
-        <v>114</v>
+        <v>151</v>
       </c>
     </row>
     <row r="93">
@@ -25327,7 +25327,7 @@
         <v>61166</v>
       </c>
       <c r="K92" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
     </row>
     <row r="93">
@@ -28784,7 +28784,7 @@
         <v>0</v>
       </c>
       <c r="E92" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F92" t="n">
         <v>500352</v>
@@ -28802,7 +28802,7 @@
         <v>66064</v>
       </c>
       <c r="K92" t="n">
-        <v>211</v>
+        <v>217</v>
       </c>
     </row>
     <row r="93">
@@ -32277,7 +32277,7 @@
         <v>54738</v>
       </c>
       <c r="K92" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="93">
@@ -35752,7 +35752,7 @@
         <v>56300</v>
       </c>
       <c r="K92" t="n">
-        <v>93</v>
+        <v>111</v>
       </c>
     </row>
     <row r="93">
@@ -39227,7 +39227,7 @@
         <v>52757</v>
       </c>
       <c r="K92" t="n">
-        <v>47</v>
+        <v>59</v>
       </c>
     </row>
     <row r="93">

--- a/estado/registroRegional.xlsx
+++ b/estado/registroRegional.xlsx
@@ -7939,7 +7939,7 @@
         <v>69208</v>
       </c>
       <c r="K92" t="n">
-        <v>457</v>
+        <v>481</v>
       </c>
     </row>
     <row r="93">
@@ -11414,7 +11414,7 @@
         <v>79222</v>
       </c>
       <c r="K92" t="n">
-        <v>559</v>
+        <v>568</v>
       </c>
     </row>
     <row r="93">
@@ -14902,7 +14902,7 @@
         <v>140348</v>
       </c>
       <c r="K92" t="n">
-        <v>17</v>
+        <v>40</v>
       </c>
     </row>
     <row r="93">
@@ -18377,7 +18377,7 @@
         <v>79201</v>
       </c>
       <c r="K92" t="n">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="93">
@@ -19355,7 +19355,7 @@
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F25" t="n">
         <v>1582242</v>
@@ -21852,7 +21852,7 @@
         <v>189012</v>
       </c>
       <c r="K92" t="n">
-        <v>151</v>
+        <v>214</v>
       </c>
     </row>
     <row r="93">
@@ -25327,7 +25327,7 @@
         <v>61166</v>
       </c>
       <c r="K92" t="n">
-        <v>16</v>
+        <v>33</v>
       </c>
     </row>
     <row r="93">
@@ -28802,7 +28802,7 @@
         <v>66064</v>
       </c>
       <c r="K92" t="n">
-        <v>217</v>
+        <v>226</v>
       </c>
     </row>
     <row r="93">
@@ -32277,7 +32277,7 @@
         <v>54738</v>
       </c>
       <c r="K92" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="93">
@@ -35752,7 +35752,7 @@
         <v>56300</v>
       </c>
       <c r="K92" t="n">
-        <v>111</v>
+        <v>125</v>
       </c>
     </row>
     <row r="93">
@@ -39227,7 +39227,7 @@
         <v>52757</v>
       </c>
       <c r="K92" t="n">
-        <v>59</v>
+        <v>66</v>
       </c>
     </row>
     <row r="93">

--- a/estado/registroRegional.xlsx
+++ b/estado/registroRegional.xlsx
@@ -7924,22 +7924,22 @@
         <v>4</v>
       </c>
       <c r="F92" t="n">
-        <v>515663</v>
+        <v>464609</v>
       </c>
       <c r="G92" t="n">
         <v>50527</v>
       </c>
       <c r="H92" t="n">
-        <v>28993</v>
+        <v>27217</v>
       </c>
       <c r="I92" s="5" t="n">
-        <v>0</v>
+        <v>-0.08876261586772471</v>
       </c>
       <c r="J92" t="n">
-        <v>69208</v>
+        <v>69226</v>
       </c>
       <c r="K92" t="n">
-        <v>481</v>
+        <v>484</v>
       </c>
     </row>
     <row r="93">
@@ -7952,16 +7952,16 @@
         <v>133520</v>
       </c>
       <c r="F93" s="6" t="n">
-        <v>295002</v>
+        <v>243948</v>
       </c>
       <c r="G93" s="6" t="n">
         <v>50527</v>
       </c>
       <c r="H93" s="6" t="n">
-        <v>28993</v>
+        <v>27217</v>
       </c>
       <c r="J93" s="6" t="n">
-        <v>69208</v>
+        <v>69226</v>
       </c>
     </row>
   </sheetData>
@@ -11396,7 +11396,7 @@
         <v>0.01318601685543943</v>
       </c>
       <c r="E92" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F92" t="n">
         <v>750284</v>
@@ -11414,7 +11414,7 @@
         <v>79222</v>
       </c>
       <c r="K92" t="n">
-        <v>568</v>
+        <v>575</v>
       </c>
     </row>
     <row r="93">
@@ -14875,16 +14875,16 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>1713695</v>
+        <v>1714859</v>
       </c>
       <c r="C92" t="n">
         <v>0</v>
       </c>
       <c r="D92" s="5" t="n">
-        <v>0.008321011465956048</v>
+        <v>0.009005897433030921</v>
       </c>
       <c r="E92" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F92" t="n">
         <v>1158193</v>
@@ -14899,10 +14899,10 @@
         <v>-0.000403471424175631</v>
       </c>
       <c r="J92" t="n">
-        <v>140348</v>
+        <v>140377</v>
       </c>
       <c r="K92" t="n">
-        <v>40</v>
+        <v>26</v>
       </c>
     </row>
     <row r="93">
@@ -14912,7 +14912,7 @@
         </is>
       </c>
       <c r="B93" s="6" t="n">
-        <v>506344</v>
+        <v>507508</v>
       </c>
       <c r="F93" s="6" t="n">
         <v>615597</v>
@@ -14924,7 +14924,7 @@
         <v>115237</v>
       </c>
       <c r="J93" s="6" t="n">
-        <v>140348</v>
+        <v>140377</v>
       </c>
     </row>
   </sheetData>
@@ -18359,25 +18359,25 @@
         <v>0.004658180367908079</v>
       </c>
       <c r="E92" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F92" t="n">
-        <v>531351</v>
+        <v>534752</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
       </c>
       <c r="H92" t="n">
-        <v>230671</v>
+        <v>231827</v>
       </c>
       <c r="I92" s="5" t="n">
-        <v>0.07341556041380243</v>
+        <v>0.07983473821812527</v>
       </c>
       <c r="J92" t="n">
         <v>79201</v>
       </c>
       <c r="K92" t="n">
-        <v>342</v>
+        <v>354</v>
       </c>
     </row>
     <row r="93">
@@ -18390,13 +18390,13 @@
         <v>89154</v>
       </c>
       <c r="F93" s="6" t="n">
-        <v>296494</v>
+        <v>299895</v>
       </c>
       <c r="G93" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H93" s="6" t="n">
-        <v>230671</v>
+        <v>231827</v>
       </c>
       <c r="J93" s="6" t="n">
         <v>79201</v>
@@ -19355,7 +19355,7 @@
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F25" t="n">
         <v>1582242</v>
@@ -21825,16 +21825,16 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>3072162</v>
+        <v>3071369</v>
       </c>
       <c r="C92" t="n">
-        <v>49144</v>
+        <v>49980</v>
       </c>
       <c r="D92" s="5" t="n">
-        <v>0.0001358590295948389</v>
+        <v>0.0001496371858980891</v>
       </c>
       <c r="E92" t="n">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="F92" t="n">
         <v>1842767</v>
@@ -21849,10 +21849,10 @@
         <v>0.0107487276447383</v>
       </c>
       <c r="J92" t="n">
-        <v>189012</v>
+        <v>189189</v>
       </c>
       <c r="K92" t="n">
-        <v>214</v>
+        <v>52</v>
       </c>
     </row>
     <row r="93">
@@ -21862,7 +21862,7 @@
         </is>
       </c>
       <c r="B93" s="6" t="n">
-        <v>736341</v>
+        <v>735548</v>
       </c>
       <c r="F93" s="6" t="n">
         <v>958303</v>
@@ -21874,7 +21874,7 @@
         <v>154953</v>
       </c>
       <c r="J93" s="6" t="n">
-        <v>189012</v>
+        <v>189189</v>
       </c>
     </row>
   </sheetData>
@@ -25309,7 +25309,7 @@
         <v>0.009256180901870761</v>
       </c>
       <c r="E92" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F92" t="n">
         <v>590365</v>
@@ -25324,10 +25324,10 @@
         <v>0</v>
       </c>
       <c r="J92" t="n">
-        <v>61166</v>
+        <v>61199</v>
       </c>
       <c r="K92" t="n">
-        <v>33</v>
+        <v>13</v>
       </c>
     </row>
     <row r="93">
@@ -25349,7 +25349,7 @@
         <v>78113</v>
       </c>
       <c r="J93" s="6" t="n">
-        <v>61166</v>
+        <v>61199</v>
       </c>
     </row>
   </sheetData>
@@ -28784,7 +28784,7 @@
         <v>0</v>
       </c>
       <c r="E92" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F92" t="n">
         <v>500352</v>
@@ -28802,7 +28802,7 @@
         <v>66064</v>
       </c>
       <c r="K92" t="n">
-        <v>226</v>
+        <v>234</v>
       </c>
     </row>
     <row r="93">
@@ -32274,10 +32274,10 @@
         <v>0</v>
       </c>
       <c r="J92" t="n">
-        <v>54738</v>
+        <v>54751</v>
       </c>
       <c r="K92" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="93">
@@ -32299,7 +32299,7 @@
         <v>50918</v>
       </c>
       <c r="J93" s="6" t="n">
-        <v>54738</v>
+        <v>54751</v>
       </c>
     </row>
   </sheetData>
@@ -34698,7 +34698,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F64" t="n">
         <v>283177</v>
@@ -35734,7 +35734,7 @@
         <v>0.0003014396758920605</v>
       </c>
       <c r="E92" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F92" t="n">
         <v>358823</v>
@@ -35749,10 +35749,10 @@
         <v>0.0312839978400981</v>
       </c>
       <c r="J92" t="n">
-        <v>56300</v>
+        <v>56309</v>
       </c>
       <c r="K92" t="n">
-        <v>125</v>
+        <v>131</v>
       </c>
     </row>
     <row r="93">
@@ -35774,7 +35774,7 @@
         <v>28881</v>
       </c>
       <c r="J93" s="6" t="n">
-        <v>56300</v>
+        <v>56309</v>
       </c>
     </row>
   </sheetData>
@@ -39200,13 +39200,13 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>510824</v>
+        <v>499821</v>
       </c>
       <c r="C92" t="n">
         <v>0</v>
       </c>
       <c r="D92" s="5" t="n">
-        <v>0</v>
+        <v>-0.02153970839271451</v>
       </c>
       <c r="E92" t="n">
         <v>1</v>
@@ -39224,10 +39224,10 @@
         <v>0</v>
       </c>
       <c r="J92" t="n">
-        <v>52757</v>
+        <v>52772</v>
       </c>
       <c r="K92" t="n">
-        <v>66</v>
+        <v>57</v>
       </c>
     </row>
     <row r="93">
@@ -39237,7 +39237,7 @@
         </is>
       </c>
       <c r="B93" s="6" t="n">
-        <v>-99901</v>
+        <v>-110904</v>
       </c>
       <c r="F93" s="6" t="n">
         <v>-7808</v>
@@ -39249,7 +39249,7 @@
         <v>72</v>
       </c>
       <c r="J93" s="6" t="n">
-        <v>52757</v>
+        <v>52772</v>
       </c>
     </row>
   </sheetData>

--- a/estado/registroRegional.xlsx
+++ b/estado/registroRegional.xlsx
@@ -7939,7 +7939,7 @@
         <v>69226</v>
       </c>
       <c r="K92" t="n">
-        <v>484</v>
+        <v>495</v>
       </c>
     </row>
     <row r="93">
@@ -11414,7 +11414,7 @@
         <v>79222</v>
       </c>
       <c r="K92" t="n">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="93">
@@ -14899,10 +14899,10 @@
         <v>-0.000403471424175631</v>
       </c>
       <c r="J92" t="n">
-        <v>140377</v>
+        <v>140401</v>
       </c>
       <c r="K92" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
     </row>
     <row r="93">
@@ -14924,7 +14924,7 @@
         <v>115237</v>
       </c>
       <c r="J93" s="6" t="n">
-        <v>140377</v>
+        <v>140401</v>
       </c>
     </row>
   </sheetData>
@@ -18359,7 +18359,7 @@
         <v>0.004658180367908079</v>
       </c>
       <c r="E92" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F92" t="n">
         <v>534752</v>
@@ -18377,7 +18377,7 @@
         <v>79201</v>
       </c>
       <c r="K92" t="n">
-        <v>354</v>
+        <v>362</v>
       </c>
     </row>
     <row r="93">
@@ -19355,7 +19355,7 @@
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F25" t="n">
         <v>1582242</v>
@@ -21834,7 +21834,7 @@
         <v>0.0001496371858980891</v>
       </c>
       <c r="E92" t="n">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="F92" t="n">
         <v>1842767</v>
@@ -21849,10 +21849,10 @@
         <v>0.0107487276447383</v>
       </c>
       <c r="J92" t="n">
-        <v>189189</v>
+        <v>189201</v>
       </c>
       <c r="K92" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="93">
@@ -21874,7 +21874,7 @@
         <v>154953</v>
       </c>
       <c r="J93" s="6" t="n">
-        <v>189189</v>
+        <v>189201</v>
       </c>
     </row>
   </sheetData>
@@ -25309,7 +25309,7 @@
         <v>0.009256180901870761</v>
       </c>
       <c r="E92" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F92" t="n">
         <v>590365</v>
@@ -25318,16 +25318,16 @@
         <v>4948</v>
       </c>
       <c r="H92" t="n">
-        <v>78113</v>
+        <v>80609</v>
       </c>
       <c r="I92" s="5" t="n">
-        <v>0</v>
+        <v>0.003706420601521177</v>
       </c>
       <c r="J92" t="n">
         <v>61199</v>
       </c>
       <c r="K92" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
     </row>
     <row r="93">
@@ -25346,7 +25346,7 @@
         <v>4948</v>
       </c>
       <c r="H93" s="6" t="n">
-        <v>78113</v>
+        <v>80609</v>
       </c>
       <c r="J93" s="6" t="n">
         <v>61199</v>
@@ -28784,7 +28784,7 @@
         <v>0</v>
       </c>
       <c r="E92" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F92" t="n">
         <v>500352</v>
@@ -28802,7 +28802,7 @@
         <v>66064</v>
       </c>
       <c r="K92" t="n">
-        <v>234</v>
+        <v>247</v>
       </c>
     </row>
     <row r="93">
@@ -32259,7 +32259,7 @@
         <v>-0.0002008701044150251</v>
       </c>
       <c r="E92" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F92" t="n">
         <v>296309</v>
@@ -32274,10 +32274,10 @@
         <v>0</v>
       </c>
       <c r="J92" t="n">
-        <v>54751</v>
+        <v>54753</v>
       </c>
       <c r="K92" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="93">
@@ -32299,7 +32299,7 @@
         <v>50918</v>
       </c>
       <c r="J93" s="6" t="n">
-        <v>54751</v>
+        <v>54753</v>
       </c>
     </row>
   </sheetData>
@@ -35734,7 +35734,7 @@
         <v>0.0003014396758920605</v>
       </c>
       <c r="E92" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F92" t="n">
         <v>358823</v>
@@ -35752,7 +35752,7 @@
         <v>56309</v>
       </c>
       <c r="K92" t="n">
-        <v>131</v>
+        <v>136</v>
       </c>
     </row>
     <row r="93">
@@ -39200,16 +39200,16 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>499821</v>
+        <v>99505</v>
       </c>
       <c r="C92" t="n">
         <v>0</v>
       </c>
       <c r="D92" s="5" t="n">
-        <v>-0.02153970839271451</v>
+        <v>-0.8052068814307863</v>
       </c>
       <c r="E92" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F92" t="n">
         <v>295759</v>
@@ -39224,10 +39224,10 @@
         <v>0</v>
       </c>
       <c r="J92" t="n">
-        <v>52772</v>
+        <v>52773</v>
       </c>
       <c r="K92" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="93">
@@ -39237,7 +39237,7 @@
         </is>
       </c>
       <c r="B93" s="6" t="n">
-        <v>-110904</v>
+        <v>-511220</v>
       </c>
       <c r="F93" s="6" t="n">
         <v>-7808</v>
@@ -39249,7 +39249,7 @@
         <v>72</v>
       </c>
       <c r="J93" s="6" t="n">
-        <v>52772</v>
+        <v>52773</v>
       </c>
     </row>
   </sheetData>

--- a/estado/registroRegional.xlsx
+++ b/estado/registroRegional.xlsx
@@ -7477,7 +7477,7 @@
         <v>0.001218784331953013</v>
       </c>
       <c r="E80" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F80" t="n">
         <v>467119</v>
@@ -7514,7 +7514,7 @@
         <v>0</v>
       </c>
       <c r="E81" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F81" t="n">
         <v>470002</v>
@@ -7924,22 +7924,22 @@
         <v>4</v>
       </c>
       <c r="F92" t="n">
-        <v>464609</v>
+        <v>514725</v>
       </c>
       <c r="G92" t="n">
         <v>50527</v>
       </c>
       <c r="H92" t="n">
-        <v>27217</v>
+        <v>28993</v>
       </c>
       <c r="I92" s="5" t="n">
-        <v>-0.08876261586772471</v>
+        <v>-0.001575985873252428</v>
       </c>
       <c r="J92" t="n">
-        <v>69226</v>
+        <v>69210</v>
       </c>
       <c r="K92" t="n">
-        <v>495</v>
+        <v>505</v>
       </c>
     </row>
     <row r="93">
@@ -7952,16 +7952,16 @@
         <v>133520</v>
       </c>
       <c r="F93" s="6" t="n">
-        <v>243948</v>
+        <v>294064</v>
       </c>
       <c r="G93" s="6" t="n">
         <v>50527</v>
       </c>
       <c r="H93" s="6" t="n">
-        <v>27217</v>
+        <v>28993</v>
       </c>
       <c r="J93" s="6" t="n">
-        <v>69226</v>
+        <v>69210</v>
       </c>
     </row>
   </sheetData>
@@ -11396,7 +11396,7 @@
         <v>0.01318601685543943</v>
       </c>
       <c r="E92" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F92" t="n">
         <v>750284</v>
@@ -11411,10 +11411,10 @@
         <v>0</v>
       </c>
       <c r="J92" t="n">
-        <v>79222</v>
+        <v>79221</v>
       </c>
       <c r="K92" t="n">
-        <v>577</v>
+        <v>592</v>
       </c>
     </row>
     <row r="93">
@@ -11436,7 +11436,7 @@
         <v>94817</v>
       </c>
       <c r="J93" s="6" t="n">
-        <v>79222</v>
+        <v>79221</v>
       </c>
     </row>
   </sheetData>
@@ -14884,7 +14884,7 @@
         <v>0.009005897433030921</v>
       </c>
       <c r="E92" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F92" t="n">
         <v>1158193</v>
@@ -14899,10 +14899,10 @@
         <v>-0.000403471424175631</v>
       </c>
       <c r="J92" t="n">
-        <v>140401</v>
+        <v>140429</v>
       </c>
       <c r="K92" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="93">
@@ -14924,7 +14924,7 @@
         <v>115237</v>
       </c>
       <c r="J93" s="6" t="n">
-        <v>140401</v>
+        <v>140429</v>
       </c>
     </row>
   </sheetData>
@@ -18377,7 +18377,7 @@
         <v>79201</v>
       </c>
       <c r="K92" t="n">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="93">
@@ -19355,7 +19355,7 @@
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F25" t="n">
         <v>1582242</v>
@@ -21834,7 +21834,7 @@
         <v>0.0001496371858980891</v>
       </c>
       <c r="E92" t="n">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="F92" t="n">
         <v>1842767</v>
@@ -21849,10 +21849,10 @@
         <v>0.0107487276447383</v>
       </c>
       <c r="J92" t="n">
-        <v>189201</v>
+        <v>189223</v>
       </c>
       <c r="K92" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="93">
@@ -21874,7 +21874,7 @@
         <v>154953</v>
       </c>
       <c r="J93" s="6" t="n">
-        <v>189201</v>
+        <v>189223</v>
       </c>
     </row>
   </sheetData>
@@ -25309,7 +25309,7 @@
         <v>0.009256180901870761</v>
       </c>
       <c r="E92" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F92" t="n">
         <v>590365</v>
@@ -25324,10 +25324,10 @@
         <v>0.003706420601521177</v>
       </c>
       <c r="J92" t="n">
-        <v>61199</v>
+        <v>61236</v>
       </c>
       <c r="K92" t="n">
-        <v>29</v>
+        <v>5</v>
       </c>
     </row>
     <row r="93">
@@ -25349,7 +25349,7 @@
         <v>80609</v>
       </c>
       <c r="J93" s="6" t="n">
-        <v>61199</v>
+        <v>61236</v>
       </c>
     </row>
   </sheetData>
@@ -28784,7 +28784,7 @@
         <v>0</v>
       </c>
       <c r="E92" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F92" t="n">
         <v>500352</v>
@@ -28802,7 +28802,7 @@
         <v>66064</v>
       </c>
       <c r="K92" t="n">
-        <v>247</v>
+        <v>251</v>
       </c>
     </row>
     <row r="93">
@@ -32259,7 +32259,7 @@
         <v>-0.0002008701044150251</v>
       </c>
       <c r="E92" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F92" t="n">
         <v>296309</v>
@@ -32274,10 +32274,10 @@
         <v>0</v>
       </c>
       <c r="J92" t="n">
-        <v>54753</v>
+        <v>54757</v>
       </c>
       <c r="K92" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="93">
@@ -32299,7 +32299,7 @@
         <v>50918</v>
       </c>
       <c r="J93" s="6" t="n">
-        <v>54753</v>
+        <v>54757</v>
       </c>
     </row>
   </sheetData>
@@ -35734,7 +35734,7 @@
         <v>0.0003014396758920605</v>
       </c>
       <c r="E92" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F92" t="n">
         <v>358823</v>
@@ -35752,7 +35752,7 @@
         <v>56309</v>
       </c>
       <c r="K92" t="n">
-        <v>136</v>
+        <v>144</v>
       </c>
     </row>
     <row r="93">
@@ -39200,16 +39200,16 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>99505</v>
+        <v>499559</v>
       </c>
       <c r="C92" t="n">
         <v>0</v>
       </c>
       <c r="D92" s="5" t="n">
-        <v>-0.8052068814307863</v>
+        <v>-0.02205260520257466</v>
       </c>
       <c r="E92" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F92" t="n">
         <v>295759</v>
@@ -39224,7 +39224,7 @@
         <v>0</v>
       </c>
       <c r="J92" t="n">
-        <v>52773</v>
+        <v>52778</v>
       </c>
       <c r="K92" t="n">
         <v>61</v>
@@ -39237,7 +39237,7 @@
         </is>
       </c>
       <c r="B93" s="6" t="n">
-        <v>-511220</v>
+        <v>-111166</v>
       </c>
       <c r="F93" s="6" t="n">
         <v>-7808</v>
@@ -39249,7 +39249,7 @@
         <v>72</v>
       </c>
       <c r="J93" s="6" t="n">
-        <v>52773</v>
+        <v>52778</v>
       </c>
     </row>
   </sheetData>

--- a/estado/registroRegional.xlsx
+++ b/estado/registroRegional.xlsx
@@ -7921,7 +7921,7 @@
         <v>0</v>
       </c>
       <c r="E92" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F92" t="n">
         <v>514725</v>
@@ -7936,10 +7936,10 @@
         <v>-0.001575985873252428</v>
       </c>
       <c r="J92" t="n">
-        <v>69210</v>
+        <v>69251</v>
       </c>
       <c r="K92" t="n">
-        <v>505</v>
+        <v>502</v>
       </c>
     </row>
     <row r="93">
@@ -7961,7 +7961,7 @@
         <v>28993</v>
       </c>
       <c r="J93" s="6" t="n">
-        <v>69210</v>
+        <v>69251</v>
       </c>
     </row>
   </sheetData>
@@ -11396,7 +11396,7 @@
         <v>0.01318601685543943</v>
       </c>
       <c r="E92" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F92" t="n">
         <v>750284</v>
@@ -11405,16 +11405,16 @@
         <v>26677</v>
       </c>
       <c r="H92" t="n">
-        <v>94817</v>
+        <v>94589</v>
       </c>
       <c r="I92" s="5" t="n">
-        <v>0</v>
+        <v>-0.0002615344732259818</v>
       </c>
       <c r="J92" t="n">
         <v>79221</v>
       </c>
       <c r="K92" t="n">
-        <v>592</v>
+        <v>617</v>
       </c>
     </row>
     <row r="93">
@@ -11433,7 +11433,7 @@
         <v>26677</v>
       </c>
       <c r="H93" s="6" t="n">
-        <v>94817</v>
+        <v>94589</v>
       </c>
       <c r="J93" s="6" t="n">
         <v>79221</v>
@@ -14884,7 +14884,7 @@
         <v>0.009005897433030921</v>
       </c>
       <c r="E92" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F92" t="n">
         <v>1158193</v>
@@ -14899,10 +14899,10 @@
         <v>-0.000403471424175631</v>
       </c>
       <c r="J92" t="n">
-        <v>140429</v>
+        <v>140427</v>
       </c>
       <c r="K92" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="93">
@@ -14924,7 +14924,7 @@
         <v>115237</v>
       </c>
       <c r="J93" s="6" t="n">
-        <v>140429</v>
+        <v>140427</v>
       </c>
     </row>
   </sheetData>
@@ -18377,7 +18377,7 @@
         <v>79201</v>
       </c>
       <c r="K92" t="n">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="93">
@@ -21834,7 +21834,7 @@
         <v>0.0001496371858980891</v>
       </c>
       <c r="E92" t="n">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="F92" t="n">
         <v>1842767</v>
@@ -21849,10 +21849,10 @@
         <v>0.0107487276447383</v>
       </c>
       <c r="J92" t="n">
-        <v>189223</v>
+        <v>189251</v>
       </c>
       <c r="K92" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="93">
@@ -21874,7 +21874,7 @@
         <v>154953</v>
       </c>
       <c r="J93" s="6" t="n">
-        <v>189223</v>
+        <v>189251</v>
       </c>
     </row>
   </sheetData>
@@ -25324,7 +25324,7 @@
         <v>0.003706420601521177</v>
       </c>
       <c r="J92" t="n">
-        <v>61236</v>
+        <v>61251</v>
       </c>
       <c r="K92" t="n">
         <v>5</v>
@@ -25349,7 +25349,7 @@
         <v>80609</v>
       </c>
       <c r="J93" s="6" t="n">
-        <v>61236</v>
+        <v>61251</v>
       </c>
     </row>
   </sheetData>
@@ -28784,7 +28784,7 @@
         <v>0</v>
       </c>
       <c r="E92" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F92" t="n">
         <v>500352</v>
@@ -28799,10 +28799,10 @@
         <v>0</v>
       </c>
       <c r="J92" t="n">
-        <v>66064</v>
+        <v>66065</v>
       </c>
       <c r="K92" t="n">
-        <v>251</v>
+        <v>264</v>
       </c>
     </row>
     <row r="93">
@@ -28824,7 +28824,7 @@
         <v>101039</v>
       </c>
       <c r="J93" s="6" t="n">
-        <v>66064</v>
+        <v>66065</v>
       </c>
     </row>
   </sheetData>
@@ -32250,13 +32250,13 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>801352</v>
+        <v>801562</v>
       </c>
       <c r="C92" t="n">
         <v>0</v>
       </c>
       <c r="D92" s="5" t="n">
-        <v>-0.0002008701044150251</v>
+        <v>6.113437960457285e-05</v>
       </c>
       <c r="E92" t="n">
         <v>11</v>
@@ -32274,7 +32274,7 @@
         <v>0</v>
       </c>
       <c r="J92" t="n">
-        <v>54757</v>
+        <v>54759</v>
       </c>
       <c r="K92" t="n">
         <v>3</v>
@@ -32287,7 +32287,7 @@
         </is>
       </c>
       <c r="B93" s="6" t="n">
-        <v>107516</v>
+        <v>107726</v>
       </c>
       <c r="F93" s="6" t="n">
         <v>189902</v>
@@ -32299,7 +32299,7 @@
         <v>50918</v>
       </c>
       <c r="J93" s="6" t="n">
-        <v>54757</v>
+        <v>54759</v>
       </c>
     </row>
   </sheetData>
@@ -35737,7 +35737,7 @@
         <v>9</v>
       </c>
       <c r="F92" t="n">
-        <v>358823</v>
+        <v>358699</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -35746,13 +35746,13 @@
         <v>28881</v>
       </c>
       <c r="I92" s="5" t="n">
-        <v>0.0312839978400981</v>
+        <v>0.03095416060413414</v>
       </c>
       <c r="J92" t="n">
-        <v>56309</v>
+        <v>56306</v>
       </c>
       <c r="K92" t="n">
-        <v>144</v>
+        <v>154</v>
       </c>
     </row>
     <row r="93">
@@ -35765,7 +35765,7 @@
         <v>255712</v>
       </c>
       <c r="F93" s="6" t="n">
-        <v>277402</v>
+        <v>277278</v>
       </c>
       <c r="G93" s="6" t="n">
         <v>0</v>
@@ -35774,7 +35774,7 @@
         <v>28881</v>
       </c>
       <c r="J93" s="6" t="n">
-        <v>56309</v>
+        <v>56306</v>
       </c>
     </row>
   </sheetData>
@@ -39224,10 +39224,10 @@
         <v>0</v>
       </c>
       <c r="J92" t="n">
-        <v>52778</v>
+        <v>52792</v>
       </c>
       <c r="K92" t="n">
-        <v>61</v>
+        <v>48</v>
       </c>
     </row>
     <row r="93">
@@ -39249,7 +39249,7 @@
         <v>72</v>
       </c>
       <c r="J93" s="6" t="n">
-        <v>52778</v>
+        <v>52792</v>
       </c>
     </row>
   </sheetData>

--- a/estado/registroRegional.xlsx
+++ b/estado/registroRegional.xlsx
@@ -7936,10 +7936,10 @@
         <v>-0.001575985873252428</v>
       </c>
       <c r="J92" t="n">
-        <v>69251</v>
+        <v>69312</v>
       </c>
       <c r="K92" t="n">
-        <v>502</v>
+        <v>456</v>
       </c>
     </row>
     <row r="93">
@@ -7961,7 +7961,7 @@
         <v>28993</v>
       </c>
       <c r="J93" s="6" t="n">
-        <v>69251</v>
+        <v>69312</v>
       </c>
     </row>
   </sheetData>
@@ -11396,7 +11396,7 @@
         <v>0.01318601685543943</v>
       </c>
       <c r="E92" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F92" t="n">
         <v>750284</v>
@@ -11414,7 +11414,7 @@
         <v>79221</v>
       </c>
       <c r="K92" t="n">
-        <v>617</v>
+        <v>622</v>
       </c>
     </row>
     <row r="93">
@@ -14884,10 +14884,10 @@
         <v>0.009005897433030921</v>
       </c>
       <c r="E92" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F92" t="n">
-        <v>1158193</v>
+        <v>1165038</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -14896,13 +14896,13 @@
         <v>115237</v>
       </c>
       <c r="I92" s="5" t="n">
-        <v>-0.000403471424175631</v>
+        <v>0.004969606199330583</v>
       </c>
       <c r="J92" t="n">
         <v>140427</v>
       </c>
       <c r="K92" t="n">
-        <v>21</v>
+        <v>38</v>
       </c>
     </row>
     <row r="93">
@@ -14915,7 +14915,7 @@
         <v>507508</v>
       </c>
       <c r="F93" s="6" t="n">
-        <v>615597</v>
+        <v>622442</v>
       </c>
       <c r="G93" s="6" t="n">
         <v>0</v>
@@ -18377,7 +18377,7 @@
         <v>79201</v>
       </c>
       <c r="K92" t="n">
-        <v>367</v>
+        <v>384</v>
       </c>
     </row>
     <row r="93">
@@ -21825,16 +21825,16 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>3071369</v>
+        <v>3071345</v>
       </c>
       <c r="C92" t="n">
-        <v>49980</v>
+        <v>50692</v>
       </c>
       <c r="D92" s="5" t="n">
-        <v>0.0001496371858980891</v>
+        <v>0.0003700876867500918</v>
       </c>
       <c r="E92" t="n">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="F92" t="n">
         <v>1842767</v>
@@ -21849,10 +21849,10 @@
         <v>0.0107487276447383</v>
       </c>
       <c r="J92" t="n">
-        <v>189251</v>
+        <v>189345</v>
       </c>
       <c r="K92" t="n">
-        <v>58</v>
+        <v>4</v>
       </c>
     </row>
     <row r="93">
@@ -21862,7 +21862,7 @@
         </is>
       </c>
       <c r="B93" s="6" t="n">
-        <v>735548</v>
+        <v>735524</v>
       </c>
       <c r="F93" s="6" t="n">
         <v>958303</v>
@@ -21874,7 +21874,7 @@
         <v>154953</v>
       </c>
       <c r="J93" s="6" t="n">
-        <v>189251</v>
+        <v>189345</v>
       </c>
     </row>
   </sheetData>
@@ -25324,10 +25324,10 @@
         <v>0.003706420601521177</v>
       </c>
       <c r="J92" t="n">
-        <v>61251</v>
+        <v>61273</v>
       </c>
       <c r="K92" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="93">
@@ -25349,7 +25349,7 @@
         <v>80609</v>
       </c>
       <c r="J93" s="6" t="n">
-        <v>61251</v>
+        <v>61273</v>
       </c>
     </row>
   </sheetData>
@@ -28784,25 +28784,25 @@
         <v>0</v>
       </c>
       <c r="E92" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F92" t="n">
-        <v>500352</v>
+        <v>499378</v>
       </c>
       <c r="G92" t="n">
         <v>6655</v>
       </c>
       <c r="H92" t="n">
-        <v>101039</v>
+        <v>102317</v>
       </c>
       <c r="I92" s="5" t="n">
-        <v>0</v>
+        <v>0.0004999621739144736</v>
       </c>
       <c r="J92" t="n">
         <v>66065</v>
       </c>
       <c r="K92" t="n">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="93">
@@ -28815,13 +28815,13 @@
         <v>92870</v>
       </c>
       <c r="F93" s="6" t="n">
-        <v>225440</v>
+        <v>224466</v>
       </c>
       <c r="G93" s="6" t="n">
         <v>6655</v>
       </c>
       <c r="H93" s="6" t="n">
-        <v>101039</v>
+        <v>102317</v>
       </c>
       <c r="J93" s="6" t="n">
         <v>66065</v>
@@ -32250,34 +32250,34 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>801562</v>
+        <v>795573</v>
       </c>
       <c r="C92" t="n">
         <v>0</v>
       </c>
       <c r="D92" s="5" t="n">
-        <v>6.113437960457285e-05</v>
+        <v>-0.007410983976554341</v>
       </c>
       <c r="E92" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F92" t="n">
-        <v>296309</v>
+        <v>297725</v>
       </c>
       <c r="G92" t="n">
         <v>83</v>
       </c>
       <c r="H92" t="n">
-        <v>50918</v>
+        <v>51058</v>
       </c>
       <c r="I92" s="5" t="n">
-        <v>0</v>
+        <v>0.004480147418732545</v>
       </c>
       <c r="J92" t="n">
         <v>54759</v>
       </c>
       <c r="K92" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="93">
@@ -32287,16 +32287,16 @@
         </is>
       </c>
       <c r="B93" s="6" t="n">
-        <v>107726</v>
+        <v>101737</v>
       </c>
       <c r="F93" s="6" t="n">
-        <v>189902</v>
+        <v>191318</v>
       </c>
       <c r="G93" s="6" t="n">
         <v>83</v>
       </c>
       <c r="H93" s="6" t="n">
-        <v>50918</v>
+        <v>51058</v>
       </c>
       <c r="J93" s="6" t="n">
         <v>54759</v>
@@ -35734,7 +35734,7 @@
         <v>0.0003014396758920605</v>
       </c>
       <c r="E92" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F92" t="n">
         <v>358699</v>
@@ -35752,7 +35752,7 @@
         <v>56306</v>
       </c>
       <c r="K92" t="n">
-        <v>154</v>
+        <v>158</v>
       </c>
     </row>
     <row r="93">
@@ -39227,7 +39227,7 @@
         <v>52792</v>
       </c>
       <c r="K92" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
     </row>
     <row r="93">
